--- a/Versão5/ARQU/Ontologia_ARQUI.xlsx
+++ b/Versão5/ARQU/Ontologia_ARQUI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D50E9AC-B1B5-494B-B2E1-7E0C8E276F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB453FE-5863-4750-9909-80D59E9D7515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12511" uniqueCount="1603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12565" uniqueCount="1613">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -4881,6 +4881,36 @@
   </si>
   <si>
     <t>diâmetro</t>
+  </si>
+  <si>
+    <t>é.emplacada.com</t>
+  </si>
+  <si>
+    <t>Projeto_01</t>
+  </si>
+  <si>
+    <t>é.usado.em</t>
+  </si>
+  <si>
+    <t>"Projeto de teste para formalização ontológica"</t>
+  </si>
+  <si>
+    <t>projeto.nome</t>
+  </si>
+  <si>
+    <t>"Nome do projeto"</t>
+  </si>
+  <si>
+    <t>projeto.etapa</t>
+  </si>
+  <si>
+    <t>"Estudo preliminar"</t>
+  </si>
+  <si>
+    <t>projeto.código</t>
+  </si>
+  <si>
+    <t>"PRJ001"</t>
   </si>
 </sst>
 </file>
@@ -5502,6 +5532,20 @@
   <dxfs count="32">
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -5525,13 +5569,6 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -5618,13 +5655,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -6434,7 +6464,7 @@
       </c>
       <c r="B18" s="32">
         <f ca="1">NOW()</f>
-        <v>46156.535683333335</v>
+        <v>46162.546072337966</v>
       </c>
       <c r="C18" s="59" t="s">
         <v>1365</v>
@@ -38869,7 +38899,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A426B82-2E19-47C6-9DDF-914E7B26E6D0}">
-  <dimension ref="A1:BC127"/>
+  <dimension ref="A1:BC128"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" style="85" customWidth="1"/>
@@ -38879,14 +38909,14 @@
     <col min="5" max="5" width="8.7109375" style="50" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" style="50" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.28515625" style="50" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" style="50" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="50" customWidth="1"/>
     <col min="9" max="9" width="6.28515625" style="50" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6" style="50" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="77.85546875" style="50" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.42578125" style="50" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5703125" style="50" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.7109375" style="50" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.140625" style="50" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" style="50" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="50" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="50" customWidth="1"/>
     <col min="16" max="16" width="12.42578125" style="50" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.28515625" style="50" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.28515625" style="50" bestFit="1" customWidth="1"/>
@@ -39098,7 +39128,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>125</v>
+        <v>1604</v>
       </c>
       <c r="C2" s="46" t="s">
         <v>1386</v>
@@ -39125,25 +39155,25 @@
         <v>86</v>
       </c>
       <c r="K2" s="45" t="s">
-        <v>494</v>
+        <v>1606</v>
       </c>
       <c r="L2" s="61" t="s">
-        <v>135</v>
+        <v>1607</v>
       </c>
       <c r="M2" s="45" t="s">
-        <v>1369</v>
+        <v>1608</v>
       </c>
       <c r="N2" s="61" t="s">
-        <v>136</v>
+        <v>1611</v>
       </c>
       <c r="O2" s="45" t="s">
-        <v>1368</v>
+        <v>1612</v>
       </c>
       <c r="P2" s="61" t="s">
-        <v>9</v>
+        <v>1609</v>
       </c>
       <c r="Q2" s="45" t="s">
-        <v>9</v>
+        <v>1610</v>
       </c>
       <c r="R2" s="61" t="s">
         <v>9</v>
@@ -39170,10 +39200,10 @@
         <v>9</v>
       </c>
       <c r="Z2" s="61" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="AA2" s="45" t="s">
-        <v>1368</v>
+        <v>9</v>
       </c>
       <c r="AB2" s="61" t="s">
         <v>9</v>
@@ -39265,16 +39295,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="C3" s="46" t="s">
         <v>1386</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>9</v>
+        <v>1605</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>9</v>
+        <v>1604</v>
       </c>
       <c r="F3" s="62" t="s">
         <v>9</v>
@@ -39292,13 +39322,13 @@
         <v>86</v>
       </c>
       <c r="K3" s="45" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="L3" s="61" t="s">
         <v>135</v>
       </c>
       <c r="M3" s="45" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="N3" s="61" t="s">
         <v>136</v>
@@ -39337,10 +39367,10 @@
         <v>9</v>
       </c>
       <c r="Z3" s="61" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="AA3" s="45" t="s">
-        <v>1368</v>
+        <v>9</v>
       </c>
       <c r="AB3" s="61" t="s">
         <v>9</v>
@@ -39432,16 +39462,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="C4" s="46" t="s">
         <v>1386</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>9</v>
+        <v>1605</v>
       </c>
       <c r="E4" s="68" t="s">
-        <v>9</v>
+        <v>1604</v>
       </c>
       <c r="F4" s="62" t="s">
         <v>9</v>
@@ -39459,7 +39489,7 @@
         <v>86</v>
       </c>
       <c r="K4" s="45" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L4" s="61" t="s">
         <v>135</v>
@@ -39504,10 +39534,10 @@
         <v>9</v>
       </c>
       <c r="Z4" s="61" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="AA4" s="45" t="s">
-        <v>1368</v>
+        <v>9</v>
       </c>
       <c r="AB4" s="61" t="s">
         <v>9</v>
@@ -39598,17 +39628,17 @@
       <c r="A5" s="84">
         <v>5</v>
       </c>
-      <c r="B5" s="78" t="s">
-        <v>497</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>1164</v>
+      <c r="B5" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>1386</v>
       </c>
       <c r="D5" s="62" t="s">
-        <v>9</v>
+        <v>1605</v>
       </c>
       <c r="E5" s="68" t="s">
-        <v>9</v>
+        <v>1604</v>
       </c>
       <c r="F5" s="62" t="s">
         <v>9</v>
@@ -39625,8 +39655,8 @@
       <c r="J5" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="47" t="s">
-        <v>140</v>
+      <c r="K5" s="45" t="s">
+        <v>495</v>
       </c>
       <c r="L5" s="61" t="s">
         <v>135</v>
@@ -39671,10 +39701,10 @@
         <v>9</v>
       </c>
       <c r="Z5" s="61" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="AA5" s="45" t="s">
-        <v>1368</v>
+        <v>9</v>
       </c>
       <c r="AB5" s="61" t="s">
         <v>9</v>
@@ -39761,15 +39791,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:55" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:55" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="84">
         <v>6</v>
       </c>
-      <c r="B6" s="79" t="s">
-        <v>499</v>
+      <c r="B6" s="78" t="s">
+        <v>497</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>1550</v>
+        <v>1164</v>
       </c>
       <c r="D6" s="62" t="s">
         <v>9</v>
@@ -39792,8 +39822,8 @@
       <c r="J6" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="42" t="s">
-        <v>450</v>
+      <c r="K6" s="47" t="s">
+        <v>140</v>
       </c>
       <c r="L6" s="61" t="s">
         <v>135</v>
@@ -39838,10 +39868,10 @@
         <v>9</v>
       </c>
       <c r="Z6" s="61" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="AA6" s="45" t="s">
-        <v>426</v>
+        <v>9</v>
       </c>
       <c r="AB6" s="61" t="s">
         <v>9</v>
@@ -39933,7 +39963,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="79" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C7" s="41" t="s">
         <v>1550</v>
@@ -39960,7 +39990,7 @@
         <v>86</v>
       </c>
       <c r="K7" s="42" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L7" s="61" t="s">
         <v>135</v>
@@ -40100,7 +40130,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="79" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>1550</v>
@@ -40127,7 +40157,7 @@
         <v>86</v>
       </c>
       <c r="K8" s="42" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L8" s="61" t="s">
         <v>135</v>
@@ -40267,7 +40297,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="79" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C9" s="41" t="s">
         <v>1550</v>
@@ -40294,7 +40324,7 @@
         <v>86</v>
       </c>
       <c r="K9" s="42" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L9" s="61" t="s">
         <v>135</v>
@@ -40434,7 +40464,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="79" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C10" s="41" t="s">
         <v>1550</v>
@@ -40461,7 +40491,7 @@
         <v>86</v>
       </c>
       <c r="K10" s="42" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L10" s="61" t="s">
         <v>135</v>
@@ -40596,12 +40626,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:55" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:55" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="84">
         <v>11</v>
       </c>
-      <c r="B11" s="78" t="s">
-        <v>504</v>
+      <c r="B11" s="79" t="s">
+        <v>503</v>
       </c>
       <c r="C11" s="41" t="s">
         <v>1550</v>
@@ -40627,8 +40657,8 @@
       <c r="J11" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="K11" s="47" t="s">
-        <v>123</v>
+      <c r="K11" s="42" t="s">
+        <v>454</v>
       </c>
       <c r="L11" s="61" t="s">
         <v>135</v>
@@ -40676,7 +40706,7 @@
         <v>87</v>
       </c>
       <c r="AA11" s="45" t="s">
-        <v>1368</v>
+        <v>426</v>
       </c>
       <c r="AB11" s="61" t="s">
         <v>9</v>
@@ -40768,7 +40798,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="78" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C12" s="41" t="s">
         <v>1550</v>
@@ -40795,7 +40825,7 @@
         <v>86</v>
       </c>
       <c r="K12" s="47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L12" s="61" t="s">
         <v>135</v>
@@ -40930,12 +40960,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:55" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:55" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="84">
         <v>13</v>
       </c>
-      <c r="B13" s="79" t="s">
-        <v>506</v>
+      <c r="B13" s="78" t="s">
+        <v>505</v>
       </c>
       <c r="C13" s="41" t="s">
         <v>1550</v>
@@ -40961,8 +40991,8 @@
       <c r="J13" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="42" t="s">
-        <v>116</v>
+      <c r="K13" s="47" t="s">
+        <v>124</v>
       </c>
       <c r="L13" s="61" t="s">
         <v>135</v>
@@ -41010,7 +41040,7 @@
         <v>87</v>
       </c>
       <c r="AA13" s="45" t="s">
-        <v>120</v>
+        <v>1368</v>
       </c>
       <c r="AB13" s="61" t="s">
         <v>9</v>
@@ -41102,7 +41132,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="79" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C14" s="41" t="s">
         <v>1550</v>
@@ -41129,7 +41159,7 @@
         <v>86</v>
       </c>
       <c r="K14" s="42" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L14" s="61" t="s">
         <v>135</v>
@@ -41269,7 +41299,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="79" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C15" s="41" t="s">
         <v>1550</v>
@@ -41296,7 +41326,7 @@
         <v>86</v>
       </c>
       <c r="K15" s="42" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L15" s="61" t="s">
         <v>135</v>
@@ -41436,7 +41466,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="79" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C16" s="41" t="s">
         <v>1550</v>
@@ -41463,7 +41493,7 @@
         <v>86</v>
       </c>
       <c r="K16" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L16" s="61" t="s">
         <v>135</v>
@@ -41603,7 +41633,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="79" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C17" s="41" t="s">
         <v>1550</v>
@@ -41630,7 +41660,7 @@
         <v>86</v>
       </c>
       <c r="K17" s="42" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="L17" s="61" t="s">
         <v>135</v>
@@ -41668,17 +41698,17 @@
       <c r="W17" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X17" s="63" t="s">
-        <v>97</v>
+      <c r="X17" s="61" t="s">
+        <v>9</v>
       </c>
       <c r="Y17" s="45" t="s">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="Z17" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA17" s="45" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="AB17" s="61" t="s">
         <v>9</v>
@@ -41770,16 +41800,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="79" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>542</v>
+        <v>1550</v>
       </c>
       <c r="D18" s="62" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="E18" s="68" t="s">
-        <v>506</v>
+        <v>9</v>
       </c>
       <c r="F18" s="62" t="s">
         <v>9</v>
@@ -41797,7 +41827,7 @@
         <v>86</v>
       </c>
       <c r="K18" s="42" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="L18" s="61" t="s">
         <v>135</v>
@@ -41812,22 +41842,22 @@
         <v>1368</v>
       </c>
       <c r="P18" s="61" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q18" s="45">
-        <v>1.1000000000000001</v>
+        <v>9</v>
+      </c>
+      <c r="Q18" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="R18" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="S18" s="75">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="S18" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="T18" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="U18" s="75">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="U18" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="V18" s="61" t="s">
         <v>9</v>
@@ -41838,14 +41868,14 @@
       <c r="X18" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="Y18" s="64" t="s">
-        <v>138</v>
+      <c r="Y18" s="45" t="s">
+        <v>128</v>
       </c>
       <c r="Z18" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA18" s="45" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="AB18" s="61" t="s">
         <v>9</v>
@@ -41937,10 +41967,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="79" t="s">
-        <v>98</v>
+        <v>498</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>1401</v>
+        <v>542</v>
       </c>
       <c r="D19" s="62" t="s">
         <v>121</v>
@@ -41963,9 +41993,8 @@
       <c r="J19" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="42" t="str">
-        <f>_xlfn.CONCAT("""","Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.",B19,"""")</f>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.25x25"</v>
+      <c r="K19" s="42" t="s">
+        <v>137</v>
       </c>
       <c r="L19" s="61" t="s">
         <v>135</v>
@@ -41989,13 +42018,13 @@
         <v>89</v>
       </c>
       <c r="S19" s="75">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T19" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U19" s="75">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="V19" s="61" t="s">
         <v>9</v>
@@ -42007,13 +42036,13 @@
         <v>97</v>
       </c>
       <c r="Y19" s="64" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="Z19" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA19" s="45" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="AB19" s="61" t="s">
         <v>9</v>
@@ -42105,7 +42134,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C20" s="41" t="s">
         <v>1401</v>
@@ -42114,7 +42143,7 @@
         <v>121</v>
       </c>
       <c r="E20" s="68" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F20" s="62" t="s">
         <v>9</v>
@@ -42132,8 +42161,8 @@
         <v>86</v>
       </c>
       <c r="K20" s="42" t="str">
-        <f t="shared" ref="K20:K34" si="0">_xlfn.CONCAT("""","Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.",B20,"""")</f>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.30x60"</v>
+        <f>_xlfn.CONCAT("""","Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.",B20,"""")</f>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.25x25"</v>
       </c>
       <c r="L20" s="61" t="s">
         <v>135</v>
@@ -42157,13 +42186,13 @@
         <v>89</v>
       </c>
       <c r="S20" s="75">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T20" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U20" s="75">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="V20" s="61" t="s">
         <v>9</v>
@@ -42175,7 +42204,7 @@
         <v>97</v>
       </c>
       <c r="Y20" s="64" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="Z20" s="61" t="s">
         <v>87</v>
@@ -42273,7 +42302,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C21" s="41" t="s">
         <v>1401</v>
@@ -42282,7 +42311,7 @@
         <v>121</v>
       </c>
       <c r="E21" s="68" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F21" s="62" t="s">
         <v>9</v>
@@ -42300,8 +42329,8 @@
         <v>86</v>
       </c>
       <c r="K21" s="42" t="str">
-        <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.50x10"</v>
+        <f t="shared" ref="K21:K35" si="0">_xlfn.CONCAT("""","Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.",B21,"""")</f>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.30x60"</v>
       </c>
       <c r="L21" s="61" t="s">
         <v>135</v>
@@ -42325,13 +42354,13 @@
         <v>89</v>
       </c>
       <c r="S21" s="75">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T21" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U21" s="75">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="V21" s="61" t="s">
         <v>9</v>
@@ -42343,7 +42372,7 @@
         <v>97</v>
       </c>
       <c r="Y21" s="64" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="Z21" s="61" t="s">
         <v>87</v>
@@ -42441,7 +42470,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="79" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C22" s="41" t="s">
         <v>1401</v>
@@ -42450,7 +42479,7 @@
         <v>121</v>
       </c>
       <c r="E22" s="68" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F22" s="62" t="s">
         <v>9</v>
@@ -42469,7 +42498,7 @@
       </c>
       <c r="K22" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.60x60"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.50x10"</v>
       </c>
       <c r="L22" s="61" t="s">
         <v>135</v>
@@ -42493,13 +42522,13 @@
         <v>89</v>
       </c>
       <c r="S22" s="75">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="T22" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U22" s="75">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="V22" s="61" t="s">
         <v>9</v>
@@ -42609,7 +42638,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="79" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C23" s="41" t="s">
         <v>1401</v>
@@ -42618,7 +42647,7 @@
         <v>121</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F23" s="62" t="s">
         <v>9</v>
@@ -42637,7 +42666,7 @@
       </c>
       <c r="K23" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.60x14"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.60x60"</v>
       </c>
       <c r="L23" s="61" t="s">
         <v>135</v>
@@ -42667,7 +42696,7 @@
         <v>90</v>
       </c>
       <c r="U23" s="75">
-        <v>14.5</v>
+        <v>60</v>
       </c>
       <c r="V23" s="61" t="s">
         <v>9</v>
@@ -42777,7 +42806,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C24" s="41" t="s">
         <v>1401</v>
@@ -42805,7 +42834,7 @@
       </c>
       <c r="K24" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.60x9"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.60x14"</v>
       </c>
       <c r="L24" s="61" t="s">
         <v>135</v>
@@ -42835,7 +42864,7 @@
         <v>90</v>
       </c>
       <c r="U24" s="75">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="V24" s="61" t="s">
         <v>9</v>
@@ -42945,7 +42974,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="79" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C25" s="41" t="s">
         <v>1401</v>
@@ -42954,7 +42983,7 @@
         <v>121</v>
       </c>
       <c r="E25" s="68" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F25" s="62" t="s">
         <v>9</v>
@@ -42973,7 +43002,7 @@
       </c>
       <c r="K25" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.60x10"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.60x9"</v>
       </c>
       <c r="L25" s="61" t="s">
         <v>135</v>
@@ -43003,7 +43032,7 @@
         <v>90</v>
       </c>
       <c r="U25" s="75">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="V25" s="61" t="s">
         <v>9</v>
@@ -43015,7 +43044,7 @@
         <v>97</v>
       </c>
       <c r="Y25" s="64" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="Z25" s="61" t="s">
         <v>87</v>
@@ -43113,7 +43142,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="79" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C26" s="41" t="s">
         <v>1401</v>
@@ -43122,7 +43151,7 @@
         <v>121</v>
       </c>
       <c r="E26" s="68" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F26" s="62" t="s">
         <v>9</v>
@@ -43141,7 +43170,7 @@
       </c>
       <c r="K26" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.70x70"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.60x10"</v>
       </c>
       <c r="L26" s="61" t="s">
         <v>135</v>
@@ -43165,13 +43194,13 @@
         <v>89</v>
       </c>
       <c r="S26" s="75">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="T26" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U26" s="75">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="V26" s="61" t="s">
         <v>9</v>
@@ -43183,7 +43212,7 @@
         <v>97</v>
       </c>
       <c r="Y26" s="64" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="Z26" s="61" t="s">
         <v>87</v>
@@ -43281,7 +43310,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="79" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>1401</v>
@@ -43309,7 +43338,7 @@
       </c>
       <c r="K27" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.80x80"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.70x70"</v>
       </c>
       <c r="L27" s="61" t="s">
         <v>135</v>
@@ -43333,13 +43362,13 @@
         <v>89</v>
       </c>
       <c r="S27" s="75">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="T27" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U27" s="75">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="V27" s="61" t="s">
         <v>9</v>
@@ -43449,7 +43478,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="79" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>1401</v>
@@ -43458,7 +43487,7 @@
         <v>121</v>
       </c>
       <c r="E28" s="68" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F28" s="62" t="s">
         <v>9</v>
@@ -43477,7 +43506,7 @@
       </c>
       <c r="K28" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.80x29"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.80x80"</v>
       </c>
       <c r="L28" s="61" t="s">
         <v>135</v>
@@ -43507,7 +43536,7 @@
         <v>90</v>
       </c>
       <c r="U28" s="75">
-        <v>29.8</v>
+        <v>80</v>
       </c>
       <c r="V28" s="61" t="s">
         <v>9</v>
@@ -43617,7 +43646,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="79" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C29" s="41" t="s">
         <v>1401</v>
@@ -43645,7 +43674,7 @@
       </c>
       <c r="K29" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.80x14"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.80x29"</v>
       </c>
       <c r="L29" s="61" t="s">
         <v>135</v>
@@ -43675,7 +43704,7 @@
         <v>90</v>
       </c>
       <c r="U29" s="75">
-        <v>14.5</v>
+        <v>29.8</v>
       </c>
       <c r="V29" s="61" t="s">
         <v>9</v>
@@ -43785,7 +43814,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="79" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C30" s="41" t="s">
         <v>1401</v>
@@ -43813,7 +43842,7 @@
       </c>
       <c r="K30" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.80x9"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.80x14"</v>
       </c>
       <c r="L30" s="61" t="s">
         <v>135</v>
@@ -43843,7 +43872,7 @@
         <v>90</v>
       </c>
       <c r="U30" s="75">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="V30" s="61" t="s">
         <v>9</v>
@@ -43953,7 +43982,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="79" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>1401</v>
@@ -43962,7 +43991,7 @@
         <v>121</v>
       </c>
       <c r="E31" s="68" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F31" s="62" t="s">
         <v>9</v>
@@ -43981,7 +44010,7 @@
       </c>
       <c r="K31" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.90x90"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.80x9"</v>
       </c>
       <c r="L31" s="61" t="s">
         <v>135</v>
@@ -44005,13 +44034,13 @@
         <v>89</v>
       </c>
       <c r="S31" s="75">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="T31" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U31" s="75">
-        <v>90</v>
+        <v>9.5</v>
       </c>
       <c r="V31" s="61" t="s">
         <v>9</v>
@@ -44121,7 +44150,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="79" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>1401</v>
@@ -44130,7 +44159,7 @@
         <v>121</v>
       </c>
       <c r="E32" s="68" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F32" s="62" t="s">
         <v>9</v>
@@ -44149,7 +44178,7 @@
       </c>
       <c r="K32" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.90x14"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.90x90"</v>
       </c>
       <c r="L32" s="61" t="s">
         <v>135</v>
@@ -44179,7 +44208,7 @@
         <v>90</v>
       </c>
       <c r="U32" s="75">
-        <v>14.5</v>
+        <v>90</v>
       </c>
       <c r="V32" s="61" t="s">
         <v>9</v>
@@ -44289,7 +44318,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="79" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C33" s="41" t="s">
         <v>1401</v>
@@ -44298,7 +44327,7 @@
         <v>121</v>
       </c>
       <c r="E33" s="68" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F33" s="62" t="s">
         <v>9</v>
@@ -44317,7 +44346,7 @@
       </c>
       <c r="K33" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.120x60"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.90x14"</v>
       </c>
       <c r="L33" s="61" t="s">
         <v>135</v>
@@ -44341,13 +44370,13 @@
         <v>89</v>
       </c>
       <c r="S33" s="75">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="T33" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U33" s="75">
-        <v>60</v>
+        <v>14.5</v>
       </c>
       <c r="V33" s="61" t="s">
         <v>9</v>
@@ -44457,7 +44486,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="79" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C34" s="41" t="s">
         <v>1401</v>
@@ -44485,7 +44514,7 @@
       </c>
       <c r="K34" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.120x29"</v>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.120x60"</v>
       </c>
       <c r="L34" s="61" t="s">
         <v>135</v>
@@ -44515,7 +44544,7 @@
         <v>90</v>
       </c>
       <c r="U34" s="75">
-        <v>29.4</v>
+        <v>60</v>
       </c>
       <c r="V34" s="61" t="s">
         <v>9</v>
@@ -44620,21 +44649,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:55" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:55" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="84">
         <v>35</v>
       </c>
-      <c r="B35" s="44" t="s">
-        <v>353</v>
+      <c r="B35" s="79" t="s">
+        <v>113</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>1549</v>
+        <v>1401</v>
       </c>
       <c r="D35" s="62" t="s">
-        <v>9</v>
+        <v>121</v>
       </c>
       <c r="E35" s="68" t="s">
-        <v>9</v>
+        <v>508</v>
       </c>
       <c r="F35" s="62" t="s">
         <v>9</v>
@@ -44651,8 +44680,9 @@
       <c r="J35" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="K35" s="42" t="s">
-        <v>354</v>
+      <c r="K35" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>"Peça para revestimento de pisos ou paredes. Deve ser colocado com paginação definida. Marca Eliane.CE.120x29"</v>
       </c>
       <c r="L35" s="61" t="s">
         <v>135</v>
@@ -44670,19 +44700,19 @@
         <v>88</v>
       </c>
       <c r="Q35" s="45">
-        <v>9</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="R35" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="S35" s="39">
-        <v>19</v>
+      <c r="S35" s="75">
+        <v>120</v>
       </c>
       <c r="T35" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="U35" s="39">
-        <v>39</v>
+      <c r="U35" s="75">
+        <v>29.4</v>
       </c>
       <c r="V35" s="61" t="s">
         <v>9</v>
@@ -44694,13 +44724,13 @@
         <v>97</v>
       </c>
       <c r="Y35" s="64" t="s">
-        <v>355</v>
+        <v>115</v>
       </c>
       <c r="Z35" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA35" s="45" t="s">
-        <v>356</v>
+        <v>114</v>
       </c>
       <c r="AB35" s="61" t="s">
         <v>9</v>
@@ -44792,7 +44822,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="44" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C36" s="41" t="s">
         <v>1549</v>
@@ -44819,7 +44849,7 @@
         <v>86</v>
       </c>
       <c r="K36" s="42" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="L36" s="61" t="s">
         <v>135</v>
@@ -44837,7 +44867,7 @@
         <v>88</v>
       </c>
       <c r="Q36" s="45">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R36" s="61" t="s">
         <v>89</v>
@@ -44959,7 +44989,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="44" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C37" s="41" t="s">
         <v>1549</v>
@@ -44986,7 +45016,7 @@
         <v>86</v>
       </c>
       <c r="K37" s="42" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="L37" s="61" t="s">
         <v>135</v>
@@ -45004,7 +45034,7 @@
         <v>88</v>
       </c>
       <c r="Q37" s="45">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R37" s="61" t="s">
         <v>89</v>
@@ -45121,12 +45151,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:55" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:55" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="84">
         <v>38</v>
       </c>
-      <c r="B38" s="80" t="s">
-        <v>361</v>
+      <c r="B38" s="44" t="s">
+        <v>359</v>
       </c>
       <c r="C38" s="41" t="s">
         <v>1549</v>
@@ -45153,7 +45183,7 @@
         <v>86</v>
       </c>
       <c r="K38" s="42" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L38" s="61" t="s">
         <v>135</v>
@@ -45171,7 +45201,7 @@
         <v>88</v>
       </c>
       <c r="Q38" s="45">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="R38" s="61" t="s">
         <v>89</v>
@@ -45183,108 +45213,108 @@
         <v>90</v>
       </c>
       <c r="U38" s="39">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="V38" s="61" t="s">
-        <v>363</v>
-      </c>
-      <c r="W38" s="39">
-        <v>2.2999999999999998</v>
+        <v>9</v>
+      </c>
+      <c r="W38" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="X38" s="63" t="s">
         <v>97</v>
       </c>
       <c r="Y38" s="64" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Z38" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="AA38" s="64" t="s">
-        <v>365</v>
+      <c r="AA38" s="45" t="s">
+        <v>356</v>
       </c>
       <c r="AB38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AC38" s="64" t="s">
+      <c r="AC38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AD38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AE38" s="64" t="s">
+      <c r="AE38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AF38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AG38" s="64" t="s">
+      <c r="AG38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AH38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AI38" s="64" t="s">
+      <c r="AI38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AJ38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AK38" s="64" t="s">
+      <c r="AK38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AL38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AM38" s="64" t="s">
+      <c r="AM38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AN38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AO38" s="64" t="s">
+      <c r="AO38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AP38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AQ38" s="64" t="s">
+      <c r="AQ38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AR38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AS38" s="64" t="s">
+      <c r="AS38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AT38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AU38" s="64" t="s">
+      <c r="AU38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AV38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AW38" s="64" t="s">
+      <c r="AW38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AX38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AY38" s="64" t="s">
+      <c r="AY38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AZ38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="BA38" s="64" t="s">
+      <c r="BA38" s="45" t="s">
         <v>9</v>
       </c>
       <c r="BB38" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="BC38" s="64" t="s">
+      <c r="BC38" s="45" t="s">
         <v>9</v>
       </c>
     </row>
@@ -45293,7 +45323,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="80" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C39" s="41" t="s">
         <v>1549</v>
@@ -45350,13 +45380,13 @@
         <v>90</v>
       </c>
       <c r="U39" s="39">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="V39" s="61" t="s">
         <v>363</v>
       </c>
-      <c r="W39" s="43">
-        <v>3.2</v>
+      <c r="W39" s="39">
+        <v>2.2999999999999998</v>
       </c>
       <c r="X39" s="63" t="s">
         <v>97</v>
@@ -45460,7 +45490,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="80" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C40" s="41" t="s">
         <v>1549</v>
@@ -45517,13 +45547,13 @@
         <v>90</v>
       </c>
       <c r="U40" s="39">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="V40" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W40" s="43">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="X40" s="63" t="s">
         <v>97</v>
@@ -45627,7 +45657,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="80" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C41" s="41" t="s">
         <v>1549</v>
@@ -45654,7 +45684,7 @@
         <v>86</v>
       </c>
       <c r="K41" s="42" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="L41" s="61" t="s">
         <v>135</v>
@@ -45672,25 +45702,25 @@
         <v>88</v>
       </c>
       <c r="Q41" s="45">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="R41" s="61" t="s">
         <v>89</v>
       </c>
       <c r="S41" s="39">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="T41" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U41" s="39">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="V41" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W41" s="43">
-        <v>2.2999999999999998</v>
+        <v>4.5</v>
       </c>
       <c r="X41" s="63" t="s">
         <v>97</v>
@@ -45794,7 +45824,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="80" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C42" s="41" t="s">
         <v>1549</v>
@@ -45845,19 +45875,19 @@
         <v>89</v>
       </c>
       <c r="S42" s="39">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="T42" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U42" s="39">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="V42" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W42" s="43">
-        <v>5.0999999999999996</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="X42" s="63" t="s">
         <v>97</v>
@@ -45961,7 +45991,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="80" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C43" s="41" t="s">
         <v>1549</v>
@@ -45988,7 +46018,7 @@
         <v>86</v>
       </c>
       <c r="K43" s="42" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="L43" s="61" t="s">
         <v>135</v>
@@ -46006,7 +46036,7 @@
         <v>88</v>
       </c>
       <c r="Q43" s="45">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="R43" s="61" t="s">
         <v>89</v>
@@ -46018,13 +46048,13 @@
         <v>90</v>
       </c>
       <c r="U43" s="39">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="V43" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W43" s="43">
-        <v>4.5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="X43" s="63" t="s">
         <v>97</v>
@@ -46128,7 +46158,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="80" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C44" s="41" t="s">
         <v>1549</v>
@@ -46185,13 +46215,13 @@
         <v>90</v>
       </c>
       <c r="U44" s="39">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="V44" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W44" s="43">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="X44" s="63" t="s">
         <v>97</v>
@@ -46295,7 +46325,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="80" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C45" s="41" t="s">
         <v>1549</v>
@@ -46322,7 +46352,7 @@
         <v>86</v>
       </c>
       <c r="K45" s="42" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L45" s="61" t="s">
         <v>135</v>
@@ -46340,7 +46370,7 @@
         <v>88</v>
       </c>
       <c r="Q45" s="45">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R45" s="61" t="s">
         <v>89</v>
@@ -46352,13 +46382,13 @@
         <v>90</v>
       </c>
       <c r="U45" s="39">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="V45" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W45" s="43">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="X45" s="63" t="s">
         <v>97</v>
@@ -46462,7 +46492,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="80" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C46" s="41" t="s">
         <v>1549</v>
@@ -46489,7 +46519,7 @@
         <v>86</v>
       </c>
       <c r="K46" s="42" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L46" s="61" t="s">
         <v>135</v>
@@ -46507,7 +46537,7 @@
         <v>88</v>
       </c>
       <c r="Q46" s="45">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="R46" s="61" t="s">
         <v>89</v>
@@ -46519,13 +46549,13 @@
         <v>90</v>
       </c>
       <c r="U46" s="39">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="V46" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W46" s="43">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="X46" s="63" t="s">
         <v>97</v>
@@ -46537,7 +46567,7 @@
         <v>87</v>
       </c>
       <c r="AA46" s="64" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="AB46" s="61" t="s">
         <v>9</v>
@@ -46629,7 +46659,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="80" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C47" s="41" t="s">
         <v>1549</v>
@@ -46686,13 +46716,13 @@
         <v>90</v>
       </c>
       <c r="U47" s="39">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="V47" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W47" s="43">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="X47" s="63" t="s">
         <v>97</v>
@@ -46796,7 +46826,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="80" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C48" s="41" t="s">
         <v>1549</v>
@@ -46853,13 +46883,13 @@
         <v>90</v>
       </c>
       <c r="U48" s="39">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="V48" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W48" s="43">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="X48" s="63" t="s">
         <v>97</v>
@@ -46963,7 +46993,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="80" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C49" s="41" t="s">
         <v>1549</v>
@@ -46990,7 +47020,7 @@
         <v>86</v>
       </c>
       <c r="K49" s="42" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="L49" s="61" t="s">
         <v>135</v>
@@ -47008,7 +47038,7 @@
         <v>88</v>
       </c>
       <c r="Q49" s="45">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="R49" s="61" t="s">
         <v>89</v>
@@ -47026,19 +47056,19 @@
         <v>363</v>
       </c>
       <c r="W49" s="43">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="X49" s="63" t="s">
         <v>97</v>
       </c>
       <c r="Y49" s="64" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="Z49" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA49" s="64" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="AB49" s="61" t="s">
         <v>9</v>
@@ -47130,7 +47160,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="80" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C50" s="41" t="s">
         <v>1549</v>
@@ -47187,13 +47217,13 @@
         <v>90</v>
       </c>
       <c r="U50" s="39">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="V50" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W50" s="43">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="X50" s="63" t="s">
         <v>97</v>
@@ -47297,7 +47327,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="80" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C51" s="41" t="s">
         <v>1549</v>
@@ -47354,13 +47384,13 @@
         <v>90</v>
       </c>
       <c r="U51" s="39">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="V51" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W51" s="43">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="X51" s="63" t="s">
         <v>97</v>
@@ -47464,7 +47494,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="80" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C52" s="41" t="s">
         <v>1549</v>
@@ -47521,13 +47551,13 @@
         <v>90</v>
       </c>
       <c r="U52" s="39">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="V52" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W52" s="43">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="X52" s="63" t="s">
         <v>97</v>
@@ -47631,7 +47661,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="80" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C53" s="41" t="s">
         <v>1549</v>
@@ -47658,7 +47688,7 @@
         <v>86</v>
       </c>
       <c r="K53" s="42" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="L53" s="61" t="s">
         <v>135</v>
@@ -47676,7 +47706,7 @@
         <v>88</v>
       </c>
       <c r="Q53" s="45">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="R53" s="61" t="s">
         <v>89</v>
@@ -47688,13 +47718,13 @@
         <v>90</v>
       </c>
       <c r="U53" s="39">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="V53" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W53" s="43">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="X53" s="63" t="s">
         <v>97</v>
@@ -47798,7 +47828,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="80" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C54" s="41" t="s">
         <v>1549</v>
@@ -47855,13 +47885,13 @@
         <v>90</v>
       </c>
       <c r="U54" s="39">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="V54" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W54" s="43">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="X54" s="63" t="s">
         <v>97</v>
@@ -47965,7 +47995,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="80" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C55" s="41" t="s">
         <v>1549</v>
@@ -48022,13 +48052,13 @@
         <v>90</v>
       </c>
       <c r="U55" s="39">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="V55" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W55" s="43">
-        <v>6.7</v>
+        <v>3.1</v>
       </c>
       <c r="X55" s="63" t="s">
         <v>97</v>
@@ -48132,7 +48162,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="80" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C56" s="41" t="s">
         <v>1549</v>
@@ -48189,13 +48219,13 @@
         <v>90</v>
       </c>
       <c r="U56" s="39">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="V56" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W56" s="43">
-        <v>4.7</v>
+        <v>6.7</v>
       </c>
       <c r="X56" s="63" t="s">
         <v>97</v>
@@ -48299,7 +48329,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="80" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C57" s="41" t="s">
         <v>1549</v>
@@ -48326,7 +48356,7 @@
         <v>86</v>
       </c>
       <c r="K57" s="42" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="L57" s="61" t="s">
         <v>135</v>
@@ -48344,7 +48374,7 @@
         <v>88</v>
       </c>
       <c r="Q57" s="45">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R57" s="61" t="s">
         <v>89</v>
@@ -48356,13 +48386,13 @@
         <v>90</v>
       </c>
       <c r="U57" s="39">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="V57" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W57" s="43">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="X57" s="63" t="s">
         <v>97</v>
@@ -48466,7 +48496,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="80" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C58" s="41" t="s">
         <v>1549</v>
@@ -48523,13 +48553,13 @@
         <v>90</v>
       </c>
       <c r="U58" s="39">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="V58" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W58" s="43">
-        <v>4.3</v>
+        <v>7.3</v>
       </c>
       <c r="X58" s="63" t="s">
         <v>97</v>
@@ -48633,7 +48663,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="80" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C59" s="41" t="s">
         <v>1549</v>
@@ -48690,13 +48720,13 @@
         <v>90</v>
       </c>
       <c r="U59" s="39">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="V59" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W59" s="43">
-        <v>8.6999999999999993</v>
+        <v>4.3</v>
       </c>
       <c r="X59" s="63" t="s">
         <v>97</v>
@@ -48800,7 +48830,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="80" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C60" s="41" t="s">
         <v>1549</v>
@@ -48857,13 +48887,13 @@
         <v>90</v>
       </c>
       <c r="U60" s="39">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="V60" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W60" s="43">
-        <v>5.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="X60" s="63" t="s">
         <v>97</v>
@@ -48962,12 +48992,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:55" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:55" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="84">
         <v>61</v>
       </c>
-      <c r="B61" s="44" t="s">
-        <v>412</v>
+      <c r="B61" s="80" t="s">
+        <v>395</v>
       </c>
       <c r="C61" s="41" t="s">
         <v>1549</v>
@@ -48994,7 +49024,7 @@
         <v>86</v>
       </c>
       <c r="K61" s="42" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="L61" s="61" t="s">
         <v>135</v>
@@ -49012,37 +49042,37 @@
         <v>88</v>
       </c>
       <c r="Q61" s="45">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="R61" s="61" t="s">
         <v>89</v>
       </c>
       <c r="S61" s="39">
-        <v>66.7</v>
+        <v>19</v>
       </c>
       <c r="T61" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U61" s="39">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="V61" s="61" t="s">
         <v>363</v>
       </c>
-      <c r="W61" s="39">
-        <v>18</v>
-      </c>
-      <c r="X61" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y61" s="45" t="s">
-        <v>9</v>
+      <c r="W61" s="43">
+        <v>5.7</v>
+      </c>
+      <c r="X61" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y61" s="64" t="s">
+        <v>355</v>
       </c>
       <c r="Z61" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="AA61" s="45" t="s">
-        <v>414</v>
+      <c r="AA61" s="64" t="s">
+        <v>365</v>
       </c>
       <c r="AB61" s="61" t="s">
         <v>9</v>
@@ -49071,61 +49101,61 @@
       <c r="AJ61" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AK61" s="45" t="s">
+      <c r="AK61" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AL61" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AM61" s="45" t="s">
+      <c r="AM61" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AN61" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AO61" s="45" t="s">
+      <c r="AO61" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AP61" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AQ61" s="45" t="s">
+      <c r="AQ61" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AR61" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AS61" s="45" t="s">
+      <c r="AS61" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AT61" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AU61" s="45" t="s">
+      <c r="AU61" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AV61" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AW61" s="45" t="s">
+      <c r="AW61" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AX61" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AY61" s="45" t="s">
+      <c r="AY61" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AZ61" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="BA61" s="45" t="s">
+      <c r="BA61" s="64" t="s">
         <v>9</v>
       </c>
       <c r="BB61" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="BC61" s="45" t="s">
+      <c r="BC61" s="64" t="s">
         <v>9</v>
       </c>
     </row>
@@ -49134,7 +49164,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="44" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C62" s="41" t="s">
         <v>1549</v>
@@ -49161,7 +49191,7 @@
         <v>86</v>
       </c>
       <c r="K62" s="42" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="L62" s="61" t="s">
         <v>135</v>
@@ -49179,25 +49209,25 @@
         <v>88</v>
       </c>
       <c r="Q62" s="45">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R62" s="61" t="s">
         <v>89</v>
       </c>
       <c r="S62" s="39">
-        <v>30</v>
+        <v>66.7</v>
       </c>
       <c r="T62" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U62" s="39">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="V62" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="W62" s="39" t="s">
-        <v>9</v>
+        <v>363</v>
+      </c>
+      <c r="W62" s="39">
+        <v>18</v>
       </c>
       <c r="X62" s="61" t="s">
         <v>9</v>
@@ -49209,7 +49239,7 @@
         <v>87</v>
       </c>
       <c r="AA62" s="45" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB62" s="61" t="s">
         <v>9</v>
@@ -49301,7 +49331,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="44" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C63" s="41" t="s">
         <v>1549</v>
@@ -49328,7 +49358,7 @@
         <v>86</v>
       </c>
       <c r="K63" s="42" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="L63" s="61" t="s">
         <v>135</v>
@@ -49346,60 +49376,60 @@
         <v>88</v>
       </c>
       <c r="Q63" s="45">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="R63" s="61" t="s">
         <v>89</v>
       </c>
       <c r="S63" s="39">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="T63" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U63" s="39">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="V63" s="61" t="s">
-        <v>363</v>
-      </c>
-      <c r="W63" s="39">
-        <v>2.6</v>
-      </c>
-      <c r="X63" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y63" s="64" t="s">
-        <v>420</v>
+        <v>9</v>
+      </c>
+      <c r="W63" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="X63" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y63" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="Z63" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA63" s="45" t="s">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="AB63" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AC63" s="45" t="s">
+      <c r="AC63" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AD63" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AE63" s="45" t="s">
+      <c r="AE63" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AF63" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AG63" s="45" t="s">
+      <c r="AG63" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AH63" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AI63" s="45" t="s">
+      <c r="AI63" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AJ63" s="61" t="s">
@@ -49468,7 +49498,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="44" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C64" s="41" t="s">
         <v>1549</v>
@@ -49495,7 +49525,7 @@
         <v>86</v>
       </c>
       <c r="K64" s="42" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L64" s="61" t="s">
         <v>135</v>
@@ -49513,19 +49543,19 @@
         <v>88</v>
       </c>
       <c r="Q64" s="45">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R64" s="61" t="s">
         <v>89</v>
       </c>
       <c r="S64" s="39">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T64" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U64" s="39">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V64" s="61" t="s">
         <v>363</v>
@@ -49533,17 +49563,17 @@
       <c r="W64" s="39">
         <v>2.6</v>
       </c>
-      <c r="X64" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y64" s="45" t="s">
-        <v>9</v>
+      <c r="X64" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y64" s="64" t="s">
+        <v>420</v>
       </c>
       <c r="Z64" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA64" s="45" t="s">
-        <v>423</v>
+        <v>378</v>
       </c>
       <c r="AB64" s="61" t="s">
         <v>9</v>
@@ -49635,7 +49665,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="44" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C65" s="41" t="s">
         <v>1549</v>
@@ -49662,7 +49692,7 @@
         <v>86</v>
       </c>
       <c r="K65" s="42" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="L65" s="61" t="s">
         <v>135</v>
@@ -49680,7 +49710,7 @@
         <v>88</v>
       </c>
       <c r="Q65" s="45">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R65" s="61" t="s">
         <v>89</v>
@@ -49695,10 +49725,10 @@
         <v>22</v>
       </c>
       <c r="V65" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="W65" s="39" t="s">
-        <v>9</v>
+        <v>363</v>
+      </c>
+      <c r="W65" s="39">
+        <v>2.6</v>
       </c>
       <c r="X65" s="61" t="s">
         <v>9</v>
@@ -49710,7 +49740,7 @@
         <v>87</v>
       </c>
       <c r="AA65" s="45" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AB65" s="61" t="s">
         <v>9</v>
@@ -49802,7 +49832,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="44" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C66" s="41" t="s">
         <v>1549</v>
@@ -49829,7 +49859,7 @@
         <v>86</v>
       </c>
       <c r="K66" s="42" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="L66" s="61" t="s">
         <v>135</v>
@@ -49859,7 +49889,7 @@
         <v>90</v>
       </c>
       <c r="U66" s="39">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="V66" s="61" t="s">
         <v>9</v>
@@ -49969,7 +49999,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="44" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C67" s="41" t="s">
         <v>1549</v>
@@ -49996,7 +50026,7 @@
         <v>86</v>
       </c>
       <c r="K67" s="42" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="L67" s="61" t="s">
         <v>135</v>
@@ -50026,7 +50056,7 @@
         <v>90</v>
       </c>
       <c r="U67" s="39">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="V67" s="61" t="s">
         <v>9</v>
@@ -50136,7 +50166,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="44" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C68" s="41" t="s">
         <v>1549</v>
@@ -50303,7 +50333,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="44" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C69" s="41" t="s">
         <v>1549</v>
@@ -50330,7 +50360,7 @@
         <v>86</v>
       </c>
       <c r="K69" s="42" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="L69" s="61" t="s">
         <v>135</v>
@@ -50465,15 +50495,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:55" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:55" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="84">
         <v>70</v>
       </c>
-      <c r="B70" s="80" t="s">
-        <v>396</v>
+      <c r="B70" s="44" t="s">
+        <v>432</v>
       </c>
       <c r="C70" s="41" t="s">
-        <v>236</v>
+        <v>1549</v>
       </c>
       <c r="D70" s="62" t="s">
         <v>9</v>
@@ -50497,7 +50527,7 @@
         <v>86</v>
       </c>
       <c r="K70" s="42" t="s">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="L70" s="61" t="s">
         <v>135</v>
@@ -50515,120 +50545,120 @@
         <v>88</v>
       </c>
       <c r="Q70" s="45">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R70" s="61" t="s">
         <v>89</v>
       </c>
       <c r="S70" s="39">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="T70" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U70" s="39">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="V70" s="61" t="s">
-        <v>363</v>
-      </c>
-      <c r="W70" s="43">
-        <v>3.5</v>
-      </c>
-      <c r="X70" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y70" s="64" t="s">
-        <v>355</v>
+        <v>9</v>
+      </c>
+      <c r="W70" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="X70" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y70" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="Z70" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="AA70" s="64" t="s">
-        <v>365</v>
+      <c r="AA70" s="45" t="s">
+        <v>426</v>
       </c>
       <c r="AB70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AC70" s="64" t="s">
+      <c r="AC70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AD70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AE70" s="64" t="s">
+      <c r="AE70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AF70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AG70" s="64" t="s">
+      <c r="AG70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AH70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AI70" s="64" t="s">
+      <c r="AI70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AJ70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AK70" s="64" t="s">
+      <c r="AK70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AL70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AM70" s="64" t="s">
+      <c r="AM70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AN70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AO70" s="64" t="s">
+      <c r="AO70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AP70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AQ70" s="64" t="s">
+      <c r="AQ70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AR70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AS70" s="64" t="s">
+      <c r="AS70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AT70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AU70" s="64" t="s">
+      <c r="AU70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AV70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AW70" s="64" t="s">
+      <c r="AW70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AX70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AY70" s="64" t="s">
+      <c r="AY70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="AZ70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="BA70" s="64" t="s">
+      <c r="BA70" s="45" t="s">
         <v>9</v>
       </c>
       <c r="BB70" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="BC70" s="64" t="s">
+      <c r="BC70" s="45" t="s">
         <v>9</v>
       </c>
     </row>
@@ -50637,7 +50667,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="80" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C71" s="41" t="s">
         <v>236</v>
@@ -50664,7 +50694,7 @@
         <v>86</v>
       </c>
       <c r="K71" s="42" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L71" s="61" t="s">
         <v>135</v>
@@ -50682,7 +50712,7 @@
         <v>88</v>
       </c>
       <c r="Q71" s="45">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="R71" s="61" t="s">
         <v>89</v>
@@ -50700,7 +50730,7 @@
         <v>363</v>
       </c>
       <c r="W71" s="43">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="X71" s="63" t="s">
         <v>97</v>
@@ -50804,7 +50834,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="80" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C72" s="41" t="s">
         <v>236</v>
@@ -50831,7 +50861,7 @@
         <v>86</v>
       </c>
       <c r="K72" s="42" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="L72" s="61" t="s">
         <v>135</v>
@@ -50849,7 +50879,7 @@
         <v>88</v>
       </c>
       <c r="Q72" s="45">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="R72" s="61" t="s">
         <v>89</v>
@@ -50867,7 +50897,7 @@
         <v>363</v>
       </c>
       <c r="W72" s="43">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="X72" s="63" t="s">
         <v>97</v>
@@ -50971,7 +51001,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="80" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C73" s="41" t="s">
         <v>236</v>
@@ -50998,7 +51028,7 @@
         <v>86</v>
       </c>
       <c r="K73" s="42" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="L73" s="61" t="s">
         <v>135</v>
@@ -51016,7 +51046,7 @@
         <v>88</v>
       </c>
       <c r="Q73" s="45">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R73" s="61" t="s">
         <v>89</v>
@@ -51034,7 +51064,7 @@
         <v>363</v>
       </c>
       <c r="W73" s="43">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="X73" s="63" t="s">
         <v>97</v>
@@ -51138,10 +51168,10 @@
         <v>74</v>
       </c>
       <c r="B74" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C74" s="41" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D74" s="62" t="s">
         <v>9</v>
@@ -51165,7 +51195,7 @@
         <v>86</v>
       </c>
       <c r="K74" s="42" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L74" s="61" t="s">
         <v>135</v>
@@ -51183,7 +51213,7 @@
         <v>88</v>
       </c>
       <c r="Q74" s="45">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="R74" s="61" t="s">
         <v>89</v>
@@ -51201,7 +51231,7 @@
         <v>363</v>
       </c>
       <c r="W74" s="43">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="X74" s="63" t="s">
         <v>97</v>
@@ -51305,7 +51335,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="80" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C75" s="41" t="s">
         <v>233</v>
@@ -51332,7 +51362,7 @@
         <v>86</v>
       </c>
       <c r="K75" s="42" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L75" s="61" t="s">
         <v>135</v>
@@ -51350,7 +51380,7 @@
         <v>88</v>
       </c>
       <c r="Q75" s="45">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="R75" s="61" t="s">
         <v>89</v>
@@ -51368,7 +51398,7 @@
         <v>363</v>
       </c>
       <c r="W75" s="43">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="X75" s="63" t="s">
         <v>97</v>
@@ -51472,7 +51502,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="80" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C76" s="41" t="s">
         <v>233</v>
@@ -51499,7 +51529,7 @@
         <v>86</v>
       </c>
       <c r="K76" s="42" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L76" s="61" t="s">
         <v>135</v>
@@ -51517,7 +51547,7 @@
         <v>88</v>
       </c>
       <c r="Q76" s="45">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="R76" s="61" t="s">
         <v>89</v>
@@ -51535,7 +51565,7 @@
         <v>363</v>
       </c>
       <c r="W76" s="43">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="X76" s="63" t="s">
         <v>97</v>
@@ -51639,7 +51669,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="80" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C77" s="41" t="s">
         <v>233</v>
@@ -51666,7 +51696,7 @@
         <v>86</v>
       </c>
       <c r="K77" s="42" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L77" s="61" t="s">
         <v>135</v>
@@ -51684,7 +51714,7 @@
         <v>88</v>
       </c>
       <c r="Q77" s="45">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R77" s="61" t="s">
         <v>89</v>
@@ -51702,7 +51732,7 @@
         <v>363</v>
       </c>
       <c r="W77" s="43">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="X77" s="63" t="s">
         <v>97</v>
@@ -51805,11 +51835,11 @@
       <c r="A78" s="84">
         <v>78</v>
       </c>
-      <c r="B78" s="79" t="s">
-        <v>165</v>
-      </c>
-      <c r="C78" s="48" t="s">
-        <v>160</v>
+      <c r="B78" s="80" t="s">
+        <v>410</v>
+      </c>
+      <c r="C78" s="41" t="s">
+        <v>233</v>
       </c>
       <c r="D78" s="62" t="s">
         <v>9</v>
@@ -51833,7 +51863,7 @@
         <v>86</v>
       </c>
       <c r="K78" s="42" t="s">
-        <v>166</v>
+        <v>411</v>
       </c>
       <c r="L78" s="61" t="s">
         <v>135</v>
@@ -51851,120 +51881,120 @@
         <v>88</v>
       </c>
       <c r="Q78" s="45">
-        <v>3.5</v>
+        <v>19</v>
       </c>
       <c r="R78" s="61" t="s">
-        <v>167</v>
-      </c>
-      <c r="S78" s="75">
-        <v>62.5</v>
+        <v>89</v>
+      </c>
+      <c r="S78" s="39">
+        <v>19</v>
       </c>
       <c r="T78" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="U78" s="75">
-        <v>125</v>
+      <c r="U78" s="39">
+        <v>29</v>
       </c>
       <c r="V78" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="W78" s="39" t="s">
-        <v>9</v>
+        <v>363</v>
+      </c>
+      <c r="W78" s="43">
+        <v>5</v>
       </c>
       <c r="X78" s="63" t="s">
         <v>97</v>
       </c>
       <c r="Y78" s="64" t="s">
-        <v>168</v>
+        <v>355</v>
       </c>
       <c r="Z78" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="AA78" s="45" t="s">
-        <v>169</v>
+      <c r="AA78" s="64" t="s">
+        <v>365</v>
       </c>
       <c r="AB78" s="61" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC78" s="45">
-        <v>0.15</v>
+        <v>9</v>
+      </c>
+      <c r="AC78" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AD78" s="61" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE78" s="45">
-        <v>0.48</v>
+        <v>9</v>
+      </c>
+      <c r="AE78" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AF78" s="61" t="s">
-        <v>172</v>
-      </c>
-      <c r="AG78" s="45">
-        <v>0.76</v>
+        <v>9</v>
+      </c>
+      <c r="AG78" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AH78" s="61" t="s">
-        <v>173</v>
-      </c>
-      <c r="AI78" s="45">
-        <v>0.86</v>
+        <v>9</v>
+      </c>
+      <c r="AI78" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AJ78" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="AK78" s="45">
-        <v>1.08</v>
+        <v>9</v>
+      </c>
+      <c r="AK78" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AL78" s="61" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM78" s="45">
-        <v>1.03</v>
+        <v>9</v>
+      </c>
+      <c r="AM78" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AN78" s="61" t="s">
-        <v>176</v>
-      </c>
-      <c r="AO78" s="45">
-        <v>0.8</v>
+        <v>9</v>
+      </c>
+      <c r="AO78" s="64" t="s">
+        <v>9</v>
       </c>
       <c r="AP78" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AQ78" s="45" t="s">
+      <c r="AQ78" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AR78" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AS78" s="45" t="s">
+      <c r="AS78" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AT78" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AU78" s="45" t="s">
+      <c r="AU78" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AV78" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AW78" s="45" t="s">
+      <c r="AW78" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AX78" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AY78" s="45" t="s">
+      <c r="AY78" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AZ78" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="BA78" s="45" t="s">
+      <c r="BA78" s="64" t="s">
         <v>9</v>
       </c>
       <c r="BB78" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="BC78" s="45" t="s">
+      <c r="BC78" s="64" t="s">
         <v>9</v>
       </c>
     </row>
@@ -51973,7 +52003,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="79" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C79" s="48" t="s">
         <v>160</v>
@@ -52024,7 +52054,7 @@
         <v>167</v>
       </c>
       <c r="S79" s="75">
-        <v>31.2</v>
+        <v>62.5</v>
       </c>
       <c r="T79" s="61" t="s">
         <v>90</v>
@@ -52140,7 +52170,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="79" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C80" s="48" t="s">
         <v>160</v>
@@ -52191,7 +52221,7 @@
         <v>167</v>
       </c>
       <c r="S80" s="75">
-        <v>15.6</v>
+        <v>31.2</v>
       </c>
       <c r="T80" s="61" t="s">
         <v>90</v>
@@ -52307,7 +52337,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="79" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C81" s="48" t="s">
         <v>160</v>
@@ -52334,7 +52364,7 @@
         <v>86</v>
       </c>
       <c r="K81" s="42" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="L81" s="61" t="s">
         <v>135</v>
@@ -52352,19 +52382,19 @@
         <v>88</v>
       </c>
       <c r="Q81" s="45">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R81" s="61" t="s">
         <v>167</v>
       </c>
       <c r="S81" s="75">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="T81" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U81" s="75">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="V81" s="61" t="s">
         <v>9</v>
@@ -52382,49 +52412,49 @@
         <v>87</v>
       </c>
       <c r="AA81" s="45" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="AB81" s="61" t="s">
         <v>170</v>
       </c>
       <c r="AC81" s="45">
-        <v>0.71</v>
+        <v>0.15</v>
       </c>
       <c r="AD81" s="61" t="s">
         <v>171</v>
       </c>
       <c r="AE81" s="45">
-        <v>1.1100000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="AF81" s="61" t="s">
         <v>172</v>
       </c>
       <c r="AG81" s="45">
-        <v>1.45</v>
+        <v>0.76</v>
       </c>
       <c r="AH81" s="61" t="s">
         <v>173</v>
       </c>
       <c r="AI81" s="45">
-        <v>2.0299999999999998</v>
+        <v>0.86</v>
       </c>
       <c r="AJ81" s="61" t="s">
         <v>174</v>
       </c>
       <c r="AK81" s="45">
-        <v>2.08</v>
+        <v>1.08</v>
       </c>
       <c r="AL81" s="61" t="s">
         <v>175</v>
       </c>
       <c r="AM81" s="45">
-        <v>1.96</v>
+        <v>1.03</v>
       </c>
       <c r="AN81" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO81" s="45" t="s">
-        <v>9</v>
+        <v>176</v>
+      </c>
+      <c r="AO81" s="45">
+        <v>0.8</v>
       </c>
       <c r="AP81" s="61" t="s">
         <v>9</v>
@@ -52474,7 +52504,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="79" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C82" s="48" t="s">
         <v>160</v>
@@ -52531,7 +52561,7 @@
         <v>90</v>
       </c>
       <c r="U82" s="75">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="V82" s="61" t="s">
         <v>9</v>
@@ -52641,7 +52671,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="79" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C83" s="48" t="s">
         <v>160</v>
@@ -52808,7 +52838,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="79" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C84" s="48" t="s">
         <v>160</v>
@@ -52859,7 +52889,7 @@
         <v>167</v>
       </c>
       <c r="S84" s="75">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T84" s="61" t="s">
         <v>90</v>
@@ -52975,7 +53005,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C85" s="48" t="s">
         <v>160</v>
@@ -53032,7 +53062,7 @@
         <v>90</v>
       </c>
       <c r="U85" s="75">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="V85" s="61" t="s">
         <v>9</v>
@@ -53142,10 +53172,10 @@
         <v>86</v>
       </c>
       <c r="B86" s="79" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C86" s="48" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D86" s="62" t="s">
         <v>9</v>
@@ -53169,7 +53199,7 @@
         <v>86</v>
       </c>
       <c r="K86" s="42" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="L86" s="61" t="s">
         <v>135</v>
@@ -53187,19 +53217,19 @@
         <v>88</v>
       </c>
       <c r="Q86" s="45">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R86" s="61" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="S86" s="75">
-        <v>62.5</v>
+        <v>40</v>
       </c>
       <c r="T86" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U86" s="75">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="V86" s="61" t="s">
         <v>9</v>
@@ -53211,55 +53241,55 @@
         <v>97</v>
       </c>
       <c r="Y86" s="64" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="Z86" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA86" s="45" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="AB86" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC86" s="45" t="s">
-        <v>9</v>
+        <v>170</v>
+      </c>
+      <c r="AC86" s="45">
+        <v>0.71</v>
       </c>
       <c r="AD86" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE86" s="45" t="s">
-        <v>9</v>
+        <v>171</v>
+      </c>
+      <c r="AE86" s="45">
+        <v>1.1100000000000001</v>
       </c>
       <c r="AF86" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG86" s="45" t="s">
-        <v>9</v>
+        <v>172</v>
+      </c>
+      <c r="AG86" s="45">
+        <v>1.45</v>
       </c>
       <c r="AH86" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI86" s="45" t="s">
-        <v>9</v>
+        <v>173</v>
+      </c>
+      <c r="AI86" s="45">
+        <v>2.0299999999999998</v>
       </c>
       <c r="AJ86" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK86" s="45" t="s">
-        <v>9</v>
+        <v>174</v>
+      </c>
+      <c r="AK86" s="45">
+        <v>2.08</v>
       </c>
       <c r="AL86" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM86" s="45" t="s">
-        <v>9</v>
+        <v>175</v>
+      </c>
+      <c r="AM86" s="45">
+        <v>1.96</v>
       </c>
       <c r="AN86" s="61" t="s">
-        <v>176</v>
-      </c>
-      <c r="AO86" s="45">
-        <v>0.85</v>
+        <v>9</v>
+      </c>
+      <c r="AO86" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AP86" s="61" t="s">
         <v>9</v>
@@ -53309,10 +53339,10 @@
         <v>87</v>
       </c>
       <c r="B87" s="79" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C87" s="48" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D87" s="62" t="s">
         <v>9</v>
@@ -53336,7 +53366,7 @@
         <v>86</v>
       </c>
       <c r="K87" s="42" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L87" s="61" t="s">
         <v>135</v>
@@ -53354,19 +53384,19 @@
         <v>88</v>
       </c>
       <c r="Q87" s="45">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R87" s="61" t="s">
         <v>89</v>
       </c>
       <c r="S87" s="75">
-        <v>120</v>
+        <v>62.5</v>
       </c>
       <c r="T87" s="61" t="s">
         <v>90</v>
       </c>
       <c r="U87" s="75">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="V87" s="61" t="s">
         <v>9</v>
@@ -53378,55 +53408,55 @@
         <v>97</v>
       </c>
       <c r="Y87" s="64" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="Z87" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA87" s="45" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AB87" s="61" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC87" s="45">
-        <v>0.71</v>
+        <v>9</v>
+      </c>
+      <c r="AC87" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AD87" s="61" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE87" s="45">
-        <v>1.1100000000000001</v>
+        <v>9</v>
+      </c>
+      <c r="AE87" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AF87" s="61" t="s">
-        <v>172</v>
-      </c>
-      <c r="AG87" s="45">
-        <v>1.45</v>
+        <v>9</v>
+      </c>
+      <c r="AG87" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AH87" s="61" t="s">
-        <v>173</v>
-      </c>
-      <c r="AI87" s="45">
-        <v>2.0299999999999998</v>
+        <v>9</v>
+      </c>
+      <c r="AI87" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AJ87" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="AK87" s="45">
-        <v>2.08</v>
+        <v>9</v>
+      </c>
+      <c r="AK87" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AL87" s="61" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM87" s="45">
-        <v>1.96</v>
+        <v>9</v>
+      </c>
+      <c r="AM87" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AN87" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO87" s="45" t="s">
-        <v>9</v>
+        <v>176</v>
+      </c>
+      <c r="AO87" s="45">
+        <v>0.85</v>
       </c>
       <c r="AP87" s="61" t="s">
         <v>9</v>
@@ -53476,10 +53506,10 @@
         <v>88</v>
       </c>
       <c r="B88" s="79" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C88" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D88" s="62" t="s">
         <v>9</v>
@@ -53503,7 +53533,7 @@
         <v>86</v>
       </c>
       <c r="K88" s="42" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L88" s="61" t="s">
         <v>135</v>
@@ -53524,13 +53554,13 @@
         <v>4</v>
       </c>
       <c r="R88" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="S88" s="39" t="s">
-        <v>9</v>
+        <v>89</v>
+      </c>
+      <c r="S88" s="75">
+        <v>120</v>
       </c>
       <c r="T88" s="61" t="s">
-        <v>1602</v>
+        <v>90</v>
       </c>
       <c r="U88" s="75">
         <v>120</v>
@@ -53643,10 +53673,10 @@
         <v>89</v>
       </c>
       <c r="B89" s="79" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C89" s="48" t="s">
-        <v>1404</v>
+        <v>162</v>
       </c>
       <c r="D89" s="62" t="s">
         <v>9</v>
@@ -53654,11 +53684,11 @@
       <c r="E89" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="F89" s="65" t="s">
-        <v>197</v>
+      <c r="F89" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="G89" s="68" t="s">
-        <v>186</v>
+        <v>9</v>
       </c>
       <c r="H89" s="62" t="s">
         <v>9</v>
@@ -53670,7 +53700,7 @@
         <v>86</v>
       </c>
       <c r="K89" s="42" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L89" s="61" t="s">
         <v>135</v>
@@ -53685,10 +53715,10 @@
         <v>1368</v>
       </c>
       <c r="P89" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q89" s="45" t="s">
-        <v>9</v>
+        <v>88</v>
+      </c>
+      <c r="Q89" s="45">
+        <v>4</v>
       </c>
       <c r="R89" s="61" t="s">
         <v>9</v>
@@ -53697,10 +53727,10 @@
         <v>9</v>
       </c>
       <c r="T89" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="U89" s="39" t="s">
-        <v>9</v>
+        <v>1602</v>
+      </c>
+      <c r="U89" s="75">
+        <v>120</v>
       </c>
       <c r="V89" s="61" t="s">
         <v>9</v>
@@ -53712,7 +53742,7 @@
         <v>97</v>
       </c>
       <c r="Y89" s="64" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="Z89" s="61" t="s">
         <v>87</v>
@@ -53721,46 +53751,46 @@
         <v>181</v>
       </c>
       <c r="AB89" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC89" s="45" t="s">
-        <v>9</v>
+        <v>170</v>
+      </c>
+      <c r="AC89" s="45">
+        <v>0.71</v>
       </c>
       <c r="AD89" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE89" s="45" t="s">
-        <v>9</v>
+        <v>171</v>
+      </c>
+      <c r="AE89" s="45">
+        <v>1.1100000000000001</v>
       </c>
       <c r="AF89" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG89" s="45" t="s">
-        <v>9</v>
+        <v>172</v>
+      </c>
+      <c r="AG89" s="45">
+        <v>1.45</v>
       </c>
       <c r="AH89" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI89" s="45" t="s">
-        <v>9</v>
+        <v>173</v>
+      </c>
+      <c r="AI89" s="45">
+        <v>2.0299999999999998</v>
       </c>
       <c r="AJ89" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK89" s="45" t="s">
-        <v>9</v>
+        <v>174</v>
+      </c>
+      <c r="AK89" s="45">
+        <v>2.08</v>
       </c>
       <c r="AL89" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM89" s="45" t="s">
-        <v>9</v>
+        <v>175</v>
+      </c>
+      <c r="AM89" s="45">
+        <v>1.96</v>
       </c>
       <c r="AN89" s="61" t="s">
-        <v>176</v>
-      </c>
-      <c r="AO89" s="45">
-        <v>0.85</v>
+        <v>9</v>
+      </c>
+      <c r="AO89" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AP89" s="61" t="s">
         <v>9</v>
@@ -53805,15 +53835,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:55" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:55" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="84">
         <v>90</v>
       </c>
-      <c r="B90" s="44" t="s">
-        <v>434</v>
-      </c>
-      <c r="C90" s="41" t="s">
-        <v>1245</v>
+      <c r="B90" s="79" t="s">
+        <v>194</v>
+      </c>
+      <c r="C90" s="48" t="s">
+        <v>1404</v>
       </c>
       <c r="D90" s="62" t="s">
         <v>9</v>
@@ -53821,11 +53851,11 @@
       <c r="E90" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="F90" s="62" t="s">
-        <v>9</v>
+      <c r="F90" s="65" t="s">
+        <v>197</v>
       </c>
       <c r="G90" s="68" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="H90" s="62" t="s">
         <v>9</v>
@@ -53836,8 +53866,8 @@
       <c r="J90" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="K90" s="45" t="s">
-        <v>435</v>
+      <c r="K90" s="42" t="s">
+        <v>195</v>
       </c>
       <c r="L90" s="61" t="s">
         <v>135</v>
@@ -53852,40 +53882,40 @@
         <v>1368</v>
       </c>
       <c r="P90" s="61" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q90" s="45">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="Q90" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="R90" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="S90" s="39">
-        <v>1.2</v>
+        <v>9</v>
+      </c>
+      <c r="S90" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="T90" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="U90" s="39">
-        <v>2.4</v>
+        <v>9</v>
+      </c>
+      <c r="U90" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="V90" s="61" t="s">
-        <v>363</v>
-      </c>
-      <c r="W90" s="39">
-        <v>31.68</v>
-      </c>
-      <c r="X90" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y90" s="45" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="W90" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="X90" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y90" s="64" t="s">
+        <v>196</v>
       </c>
       <c r="Z90" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA90" s="45" t="s">
-        <v>436</v>
+        <v>181</v>
       </c>
       <c r="AB90" s="61" t="s">
         <v>9</v>
@@ -53924,10 +53954,10 @@
         <v>9</v>
       </c>
       <c r="AN90" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO90" s="45" t="s">
-        <v>9</v>
+        <v>176</v>
+      </c>
+      <c r="AO90" s="45">
+        <v>0.85</v>
       </c>
       <c r="AP90" s="61" t="s">
         <v>9</v>
@@ -53977,16 +54007,16 @@
         <v>91</v>
       </c>
       <c r="B91" s="44" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C91" s="41" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="D91" s="62" t="s">
-        <v>9</v>
+        <v>458</v>
       </c>
       <c r="E91" s="68" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="F91" s="62" t="s">
         <v>9</v>
@@ -54004,7 +54034,7 @@
         <v>86</v>
       </c>
       <c r="K91" s="45" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="L91" s="61" t="s">
         <v>135</v>
@@ -54022,7 +54052,7 @@
         <v>88</v>
       </c>
       <c r="Q91" s="45">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="R91" s="61" t="s">
         <v>89</v>
@@ -54040,7 +54070,7 @@
         <v>363</v>
       </c>
       <c r="W91" s="39">
-        <v>34.56</v>
+        <v>31.68</v>
       </c>
       <c r="X91" s="61" t="s">
         <v>9</v>
@@ -54144,16 +54174,16 @@
         <v>92</v>
       </c>
       <c r="B92" s="44" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C92" s="41" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="D92" s="62" t="s">
-        <v>9</v>
+        <v>458</v>
       </c>
       <c r="E92" s="68" t="s">
-        <v>9</v>
+        <v>463</v>
       </c>
       <c r="F92" s="62" t="s">
         <v>9</v>
@@ -54171,7 +54201,7 @@
         <v>86</v>
       </c>
       <c r="K92" s="45" t="s">
-        <v>735</v>
+        <v>438</v>
       </c>
       <c r="L92" s="61" t="s">
         <v>135</v>
@@ -54189,7 +54219,7 @@
         <v>88</v>
       </c>
       <c r="Q92" s="45">
-        <v>35</v>
+        <v>12.5</v>
       </c>
       <c r="R92" s="61" t="s">
         <v>89</v>
@@ -54201,13 +54231,13 @@
         <v>90</v>
       </c>
       <c r="U92" s="39">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="V92" s="61" t="s">
         <v>363</v>
       </c>
       <c r="W92" s="39">
-        <v>22</v>
+        <v>34.56</v>
       </c>
       <c r="X92" s="61" t="s">
         <v>9</v>
@@ -54219,7 +54249,7 @@
         <v>87</v>
       </c>
       <c r="AA92" s="45" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="AB92" s="61" t="s">
         <v>9</v>
@@ -54311,16 +54341,16 @@
         <v>93</v>
       </c>
       <c r="B93" s="44" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C93" s="41" t="s">
-        <v>297</v>
+        <v>1247</v>
       </c>
       <c r="D93" s="62" t="s">
-        <v>9</v>
+        <v>458</v>
       </c>
       <c r="E93" s="68" t="s">
-        <v>9</v>
+        <v>465</v>
       </c>
       <c r="F93" s="62" t="s">
         <v>9</v>
@@ -54338,7 +54368,7 @@
         <v>86</v>
       </c>
       <c r="K93" s="45" t="s">
-        <v>442</v>
+        <v>735</v>
       </c>
       <c r="L93" s="61" t="s">
         <v>135</v>
@@ -54356,25 +54386,25 @@
         <v>88</v>
       </c>
       <c r="Q93" s="45">
+        <v>35</v>
+      </c>
+      <c r="R93" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="S93" s="39">
         <v>1.2</v>
       </c>
-      <c r="R93" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="S93" s="39" t="s">
-        <v>9</v>
-      </c>
       <c r="T93" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="U93" s="39" t="s">
-        <v>9</v>
+        <v>90</v>
+      </c>
+      <c r="U93" s="39">
+        <v>2.11</v>
       </c>
       <c r="V93" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="W93" s="39" t="s">
-        <v>9</v>
+        <v>363</v>
+      </c>
+      <c r="W93" s="39">
+        <v>22</v>
       </c>
       <c r="X93" s="61" t="s">
         <v>9</v>
@@ -54386,7 +54416,7 @@
         <v>87</v>
       </c>
       <c r="AA93" s="45" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AB93" s="61" t="s">
         <v>9</v>
@@ -54478,10 +54508,10 @@
         <v>94</v>
       </c>
       <c r="B94" s="44" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C94" s="41" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="D94" s="62" t="s">
         <v>9</v>
@@ -54505,7 +54535,7 @@
         <v>86</v>
       </c>
       <c r="K94" s="45" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="L94" s="61" t="s">
         <v>135</v>
@@ -54523,19 +54553,19 @@
         <v>88</v>
       </c>
       <c r="Q94" s="45">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="R94" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="S94" s="39">
-        <v>1.2</v>
+        <v>9</v>
+      </c>
+      <c r="S94" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="T94" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="U94" s="39">
-        <v>1.2</v>
+        <v>9</v>
+      </c>
+      <c r="U94" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="V94" s="61" t="s">
         <v>9</v>
@@ -54543,23 +54573,23 @@
       <c r="W94" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X94" s="63" t="s">
-        <v>97</v>
+      <c r="X94" s="61" t="s">
+        <v>9</v>
       </c>
       <c r="Y94" s="45" t="s">
-        <v>446</v>
+        <v>9</v>
       </c>
       <c r="Z94" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA94" s="45" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="AB94" s="61" t="s">
-        <v>448</v>
-      </c>
-      <c r="AC94" s="45">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="AC94" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AD94" s="61" t="s">
         <v>9</v>
@@ -54645,10 +54675,10 @@
         <v>95</v>
       </c>
       <c r="B95" s="44" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C95" s="41" t="s">
-        <v>1249</v>
+        <v>309</v>
       </c>
       <c r="D95" s="62" t="s">
         <v>9</v>
@@ -54672,7 +54702,7 @@
         <v>86</v>
       </c>
       <c r="K95" s="45" t="s">
-        <v>734</v>
+        <v>445</v>
       </c>
       <c r="L95" s="61" t="s">
         <v>135</v>
@@ -54687,22 +54717,22 @@
         <v>1368</v>
       </c>
       <c r="P95" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q95" s="45" t="s">
-        <v>9</v>
+        <v>88</v>
+      </c>
+      <c r="Q95" s="45">
+        <v>0.8</v>
       </c>
       <c r="R95" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="S95" s="39" t="s">
-        <v>9</v>
+        <v>89</v>
+      </c>
+      <c r="S95" s="39">
+        <v>1.2</v>
       </c>
       <c r="T95" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="U95" s="39" t="s">
-        <v>9</v>
+        <v>90</v>
+      </c>
+      <c r="U95" s="39">
+        <v>1.2</v>
       </c>
       <c r="V95" s="61" t="s">
         <v>9</v>
@@ -54710,23 +54740,23 @@
       <c r="W95" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X95" s="61" t="s">
-        <v>9</v>
+      <c r="X95" s="63" t="s">
+        <v>97</v>
       </c>
       <c r="Y95" s="45" t="s">
-        <v>9</v>
+        <v>446</v>
       </c>
       <c r="Z95" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA95" s="45" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AB95" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC95" s="45" t="s">
-        <v>9</v>
+        <v>448</v>
+      </c>
+      <c r="AC95" s="45">
+        <v>2</v>
       </c>
       <c r="AD95" s="61" t="s">
         <v>9</v>
@@ -54807,15 +54837,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:55" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:55" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="84">
         <v>96</v>
       </c>
-      <c r="B96" s="79" t="s">
-        <v>672</v>
+      <c r="B96" s="44" t="s">
+        <v>449</v>
       </c>
       <c r="C96" s="41" t="s">
-        <v>150</v>
+        <v>1249</v>
       </c>
       <c r="D96" s="62" t="s">
         <v>9</v>
@@ -54838,8 +54868,8 @@
       <c r="J96" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="K96" s="42" t="s">
-        <v>455</v>
+      <c r="K96" s="45" t="s">
+        <v>734</v>
       </c>
       <c r="L96" s="61" t="s">
         <v>135</v>
@@ -54854,82 +54884,82 @@
         <v>1368</v>
       </c>
       <c r="P96" s="61" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q96" s="45">
-        <v>1.6</v>
+        <v>9</v>
+      </c>
+      <c r="Q96" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="R96" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="S96" s="75">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="S96" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="T96" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="U96" s="75">
-        <v>243</v>
+        <v>9</v>
+      </c>
+      <c r="U96" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="V96" s="61" t="s">
-        <v>363</v>
-      </c>
-      <c r="W96" s="39">
-        <v>11</v>
-      </c>
-      <c r="X96" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y96" s="64" t="s">
-        <v>456</v>
+        <v>9</v>
+      </c>
+      <c r="W96" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="X96" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y96" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="Z96" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA96" s="45" t="s">
-        <v>169</v>
+        <v>443</v>
       </c>
       <c r="AB96" s="61" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC96" s="45">
-        <v>0.41</v>
+        <v>9</v>
+      </c>
+      <c r="AC96" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AD96" s="61" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE96" s="45">
-        <v>1.02</v>
+        <v>9</v>
+      </c>
+      <c r="AE96" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AF96" s="61" t="s">
-        <v>172</v>
-      </c>
-      <c r="AG96" s="45">
-        <v>0.9</v>
+        <v>9</v>
+      </c>
+      <c r="AG96" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AH96" s="61" t="s">
-        <v>173</v>
-      </c>
-      <c r="AI96" s="45">
-        <v>0.7</v>
+        <v>9</v>
+      </c>
+      <c r="AI96" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AJ96" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="AK96" s="45">
-        <v>0.47</v>
+        <v>9</v>
+      </c>
+      <c r="AK96" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AL96" s="61" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM96" s="45">
-        <v>0.44</v>
+        <v>9</v>
+      </c>
+      <c r="AM96" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AN96" s="61" t="s">
-        <v>176</v>
-      </c>
-      <c r="AO96" s="45">
-        <v>0.8</v>
+        <v>9</v>
+      </c>
+      <c r="AO96" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AP96" s="61" t="s">
         <v>9</v>
@@ -54979,7 +55009,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="79" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C97" s="41" t="s">
         <v>150</v>
@@ -55006,7 +55036,7 @@
         <v>86</v>
       </c>
       <c r="K97" s="42" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L97" s="61" t="s">
         <v>135</v>
@@ -55036,7 +55066,7 @@
         <v>90</v>
       </c>
       <c r="U97" s="75">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="V97" s="61" t="s">
         <v>363</v>
@@ -55060,43 +55090,43 @@
         <v>170</v>
       </c>
       <c r="AC97" s="45">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="AD97" s="61" t="s">
         <v>171</v>
       </c>
       <c r="AE97" s="45">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="AF97" s="61" t="s">
         <v>172</v>
       </c>
       <c r="AG97" s="45">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="AH97" s="61" t="s">
         <v>173</v>
       </c>
       <c r="AI97" s="45">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="AJ97" s="61" t="s">
         <v>174</v>
       </c>
       <c r="AK97" s="45">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="AL97" s="61" t="s">
         <v>175</v>
       </c>
       <c r="AM97" s="45">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="AN97" s="61" t="s">
         <v>176</v>
       </c>
       <c r="AO97" s="45">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AP97" s="61" t="s">
         <v>9</v>
@@ -55141,21 +55171,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:55" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:55" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="84">
         <v>98</v>
       </c>
-      <c r="B98" s="44" t="s">
-        <v>461</v>
+      <c r="B98" s="79" t="s">
+        <v>673</v>
       </c>
       <c r="C98" s="41" t="s">
-        <v>660</v>
+        <v>150</v>
       </c>
       <c r="D98" s="62" t="s">
-        <v>458</v>
-      </c>
-      <c r="E98" s="69" t="s">
-        <v>437</v>
+        <v>9</v>
+      </c>
+      <c r="E98" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="F98" s="62" t="s">
         <v>9</v>
@@ -55172,98 +55202,98 @@
       <c r="J98" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="K98" s="45" t="s">
-        <v>462</v>
+      <c r="K98" s="42" t="s">
+        <v>457</v>
       </c>
       <c r="L98" s="61" t="s">
         <v>135</v>
       </c>
       <c r="M98" s="45" t="s">
-        <v>459</v>
+        <v>1368</v>
       </c>
       <c r="N98" s="61" t="s">
         <v>136</v>
       </c>
       <c r="O98" s="45" t="s">
-        <v>460</v>
+        <v>1368</v>
       </c>
       <c r="P98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q98" s="45" t="s">
-        <v>9</v>
+        <v>88</v>
+      </c>
+      <c r="Q98" s="45">
+        <v>1.6</v>
       </c>
       <c r="R98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="S98" s="39" t="s">
-        <v>9</v>
+        <v>89</v>
+      </c>
+      <c r="S98" s="75">
+        <v>16</v>
       </c>
       <c r="T98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="U98" s="39" t="s">
-        <v>9</v>
+        <v>90</v>
+      </c>
+      <c r="U98" s="75">
+        <v>274</v>
       </c>
       <c r="V98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="W98" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="X98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y98" s="45" t="s">
-        <v>9</v>
+        <v>363</v>
+      </c>
+      <c r="W98" s="39">
+        <v>11</v>
+      </c>
+      <c r="X98" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y98" s="64" t="s">
+        <v>456</v>
       </c>
       <c r="Z98" s="61" t="s">
         <v>87</v>
       </c>
       <c r="AA98" s="45" t="s">
-        <v>426</v>
+        <v>169</v>
       </c>
       <c r="AB98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC98" s="45" t="s">
-        <v>9</v>
+        <v>170</v>
+      </c>
+      <c r="AC98" s="45">
+        <v>0.45</v>
       </c>
       <c r="AD98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE98" s="45" t="s">
-        <v>9</v>
+        <v>171</v>
+      </c>
+      <c r="AE98" s="45">
+        <v>0.96</v>
       </c>
       <c r="AF98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG98" s="45" t="s">
-        <v>9</v>
+        <v>172</v>
+      </c>
+      <c r="AG98" s="45">
+        <v>0.92</v>
       </c>
       <c r="AH98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI98" s="45" t="s">
-        <v>9</v>
+        <v>173</v>
+      </c>
+      <c r="AI98" s="45">
+        <v>0.62</v>
       </c>
       <c r="AJ98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK98" s="45" t="s">
-        <v>9</v>
+        <v>174</v>
+      </c>
+      <c r="AK98" s="45">
+        <v>0.41</v>
       </c>
       <c r="AL98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM98" s="45" t="s">
-        <v>9</v>
+        <v>175</v>
+      </c>
+      <c r="AM98" s="45">
+        <v>0.41</v>
       </c>
       <c r="AN98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO98" s="45" t="s">
-        <v>9</v>
+        <v>176</v>
+      </c>
+      <c r="AO98" s="45">
+        <v>0.75</v>
       </c>
       <c r="AP98" s="61" t="s">
         <v>9</v>
@@ -55313,13 +55343,13 @@
         <v>99</v>
       </c>
       <c r="B99" s="44" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C99" s="41" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D99" s="62" t="s">
-        <v>458</v>
+        <v>1603</v>
       </c>
       <c r="E99" s="69" t="s">
         <v>437</v>
@@ -55340,7 +55370,7 @@
         <v>86</v>
       </c>
       <c r="K99" s="45" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L99" s="61" t="s">
         <v>135</v>
@@ -55480,16 +55510,16 @@
         <v>100</v>
       </c>
       <c r="B100" s="44" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C100" s="41" t="s">
-        <v>725</v>
+        <v>661</v>
       </c>
       <c r="D100" s="62" t="s">
-        <v>458</v>
+        <v>1603</v>
       </c>
       <c r="E100" s="69" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F100" s="62" t="s">
         <v>9</v>
@@ -55507,7 +55537,7 @@
         <v>86</v>
       </c>
       <c r="K100" s="45" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="L100" s="61" t="s">
         <v>135</v>
@@ -55647,16 +55677,16 @@
         <v>101</v>
       </c>
       <c r="B101" s="44" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C101" s="41" t="s">
-        <v>664</v>
+        <v>725</v>
       </c>
       <c r="D101" s="62" t="s">
-        <v>458</v>
+        <v>1603</v>
       </c>
       <c r="E101" s="69" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F101" s="62" t="s">
         <v>9</v>
@@ -55674,7 +55704,7 @@
         <v>86</v>
       </c>
       <c r="K101" s="45" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="L101" s="61" t="s">
         <v>135</v>
@@ -55814,16 +55844,16 @@
         <v>102</v>
       </c>
       <c r="B102" s="44" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C102" s="41" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D102" s="62" t="s">
         <v>458</v>
       </c>
       <c r="E102" s="69" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="F102" s="62" t="s">
         <v>9</v>
@@ -55841,7 +55871,7 @@
         <v>86</v>
       </c>
       <c r="K102" s="45" t="s">
-        <v>733</v>
+        <v>468</v>
       </c>
       <c r="L102" s="61" t="s">
         <v>135</v>
@@ -55981,34 +56011,34 @@
         <v>103</v>
       </c>
       <c r="B103" s="44" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C103" s="41" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="D103" s="62" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="E103" s="69" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="F103" s="62" t="s">
-        <v>473</v>
-      </c>
-      <c r="G103" s="69" t="s">
-        <v>421</v>
+        <v>9</v>
+      </c>
+      <c r="G103" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="H103" s="62" t="s">
-        <v>474</v>
+        <v>9</v>
       </c>
       <c r="I103" s="68" t="s">
-        <v>104</v>
+        <v>9</v>
       </c>
       <c r="J103" s="61" t="s">
         <v>86</v>
       </c>
       <c r="K103" s="45" t="s">
-        <v>471</v>
+        <v>733</v>
       </c>
       <c r="L103" s="61" t="s">
         <v>135</v>
@@ -56047,10 +56077,10 @@
         <v>9</v>
       </c>
       <c r="X103" s="61" t="s">
-        <v>475</v>
-      </c>
-      <c r="Y103" s="45">
-        <v>60</v>
+        <v>9</v>
+      </c>
+      <c r="Y103" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="Z103" s="61" t="s">
         <v>87</v>
@@ -56148,7 +56178,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="44" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C104" s="41" t="s">
         <v>656</v>
@@ -56160,7 +56190,7 @@
         <v>421</v>
       </c>
       <c r="F104" s="62" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="G104" s="69" t="s">
         <v>421</v>
@@ -56175,7 +56205,7 @@
         <v>86</v>
       </c>
       <c r="K104" s="45" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="L104" s="61" t="s">
         <v>135</v>
@@ -56217,7 +56247,7 @@
         <v>475</v>
       </c>
       <c r="Y104" s="45">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="Z104" s="61" t="s">
         <v>87</v>
@@ -56315,7 +56345,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="44" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C105" s="41" t="s">
         <v>656</v>
@@ -56324,13 +56354,13 @@
         <v>472</v>
       </c>
       <c r="E105" s="69" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F105" s="62" t="s">
         <v>478</v>
       </c>
       <c r="G105" s="69" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="H105" s="62" t="s">
         <v>474</v>
@@ -56482,7 +56512,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="44" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C106" s="41" t="s">
         <v>656</v>
@@ -56490,26 +56520,26 @@
       <c r="D106" s="62" t="s">
         <v>472</v>
       </c>
-      <c r="E106" s="70" t="s">
-        <v>380</v>
+      <c r="E106" s="69" t="s">
+        <v>418</v>
       </c>
       <c r="F106" s="62" t="s">
-        <v>473</v>
-      </c>
-      <c r="G106" s="70" t="s">
-        <v>380</v>
+        <v>478</v>
+      </c>
+      <c r="G106" s="69" t="s">
+        <v>418</v>
       </c>
       <c r="H106" s="62" t="s">
-        <v>9</v>
+        <v>474</v>
       </c>
       <c r="I106" s="68" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="J106" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="K106" s="42" t="s">
-        <v>481</v>
+      <c r="K106" s="45" t="s">
+        <v>477</v>
       </c>
       <c r="L106" s="61" t="s">
         <v>135</v>
@@ -56548,10 +56578,10 @@
         <v>9</v>
       </c>
       <c r="X106" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y106" s="45" t="s">
-        <v>9</v>
+        <v>475</v>
+      </c>
+      <c r="Y106" s="45">
+        <v>120</v>
       </c>
       <c r="Z106" s="61" t="s">
         <v>87</v>
@@ -56649,7 +56679,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="44" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C107" s="41" t="s">
         <v>656</v>
@@ -56816,7 +56846,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="44" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C108" s="41" t="s">
         <v>656</v>
@@ -56983,7 +57013,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="44" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C109" s="41" t="s">
         <v>656</v>
@@ -57150,7 +57180,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="44" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C110" s="41" t="s">
         <v>656</v>
@@ -57177,7 +57207,7 @@
         <v>86</v>
       </c>
       <c r="K110" s="42" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="L110" s="61" t="s">
         <v>135</v>
@@ -57317,7 +57347,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C111" s="41" t="s">
         <v>656</v>
@@ -57484,7 +57514,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C112" s="41" t="s">
         <v>656</v>
@@ -57651,7 +57681,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="44" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C113" s="41" t="s">
         <v>656</v>
@@ -57818,7 +57848,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="44" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C114" s="41" t="s">
         <v>656</v>
@@ -57826,14 +57856,14 @@
       <c r="D114" s="62" t="s">
         <v>472</v>
       </c>
-      <c r="E114" s="69" t="s">
-        <v>412</v>
+      <c r="E114" s="70" t="s">
+        <v>380</v>
       </c>
       <c r="F114" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="G114" s="68" t="s">
-        <v>9</v>
+        <v>473</v>
+      </c>
+      <c r="G114" s="70" t="s">
+        <v>380</v>
       </c>
       <c r="H114" s="62" t="s">
         <v>9</v>
@@ -57845,7 +57875,7 @@
         <v>86</v>
       </c>
       <c r="K114" s="42" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="L114" s="61" t="s">
         <v>135</v>
@@ -57985,7 +58015,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="44" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C115" s="41" t="s">
         <v>656</v>
@@ -57994,7 +58024,7 @@
         <v>472</v>
       </c>
       <c r="E115" s="69" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F115" s="62" t="s">
         <v>9</v>
@@ -58012,7 +58042,7 @@
         <v>86</v>
       </c>
       <c r="K115" s="42" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="L115" s="61" t="s">
         <v>135</v>
@@ -58147,21 +58177,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:55" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:55" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="84">
         <v>116</v>
       </c>
-      <c r="B116" s="80" t="s">
-        <v>1554</v>
-      </c>
-      <c r="C116" s="81" t="s">
-        <v>920</v>
+      <c r="B116" s="44" t="s">
+        <v>492</v>
+      </c>
+      <c r="C116" s="41" t="s">
+        <v>656</v>
       </c>
       <c r="D116" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" s="68" t="s">
-        <v>9</v>
+        <v>472</v>
+      </c>
+      <c r="E116" s="69" t="s">
+        <v>415</v>
       </c>
       <c r="F116" s="62" t="s">
         <v>9</v>
@@ -58175,41 +58205,41 @@
       <c r="I116" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="J116" s="63" t="s">
+      <c r="J116" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="K116" s="64" t="s">
-        <v>1557</v>
+      <c r="K116" s="42" t="s">
+        <v>493</v>
       </c>
       <c r="L116" s="61" t="s">
         <v>135</v>
       </c>
-      <c r="M116" s="64" t="s">
-        <v>1597</v>
+      <c r="M116" s="45" t="s">
+        <v>459</v>
       </c>
       <c r="N116" s="61" t="s">
         <v>136</v>
       </c>
       <c r="O116" s="45" t="s">
-        <v>1598</v>
-      </c>
-      <c r="P116" s="63" t="s">
-        <v>1558</v>
-      </c>
-      <c r="Q116" s="64" t="s">
-        <v>1559</v>
-      </c>
-      <c r="R116" s="63" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S116" s="43">
-        <v>4</v>
-      </c>
-      <c r="T116" s="63" t="s">
-        <v>1555</v>
-      </c>
-      <c r="U116" s="43" t="s">
-        <v>1556</v>
+        <v>460</v>
+      </c>
+      <c r="P116" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q116" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="R116" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="S116" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="T116" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="U116" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="V116" s="61" t="s">
         <v>9</v>
@@ -58227,19 +58257,19 @@
         <v>87</v>
       </c>
       <c r="AA116" s="45" t="s">
-        <v>1596</v>
-      </c>
-      <c r="AB116" s="63" t="s">
-        <v>1561</v>
-      </c>
-      <c r="AC116" s="64">
-        <v>550</v>
-      </c>
-      <c r="AD116" s="63" t="s">
-        <v>1562</v>
-      </c>
-      <c r="AE116" s="64">
-        <v>0</v>
+        <v>426</v>
+      </c>
+      <c r="AB116" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC116" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD116" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE116" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AF116" s="61" t="s">
         <v>9</v>
@@ -58271,11 +58301,11 @@
       <c r="AO116" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="AP116" s="63" t="s">
-        <v>1563</v>
-      </c>
-      <c r="AQ116" s="64" t="s">
-        <v>1599</v>
+      <c r="AP116" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ116" s="45" t="s">
+        <v>9</v>
       </c>
       <c r="AR116" s="61" t="s">
         <v>9</v>
@@ -58319,7 +58349,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="80" t="s">
-        <v>1564</v>
+        <v>1554</v>
       </c>
       <c r="C117" s="81" t="s">
         <v>920</v>
@@ -58346,7 +58376,7 @@
         <v>86</v>
       </c>
       <c r="K117" s="64" t="s">
-        <v>1566</v>
+        <v>1557</v>
       </c>
       <c r="L117" s="61" t="s">
         <v>135</v>
@@ -58364,7 +58394,7 @@
         <v>1558</v>
       </c>
       <c r="Q117" s="64" t="s">
-        <v>1567</v>
+        <v>1559</v>
       </c>
       <c r="R117" s="63" t="s">
         <v>1560</v>
@@ -58376,7 +58406,7 @@
         <v>1555</v>
       </c>
       <c r="U117" s="43" t="s">
-        <v>1565</v>
+        <v>1556</v>
       </c>
       <c r="V117" s="61" t="s">
         <v>9</v>
@@ -58400,7 +58430,7 @@
         <v>1561</v>
       </c>
       <c r="AC117" s="64">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="AD117" s="63" t="s">
         <v>1562</v>
@@ -58486,7 +58516,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="80" t="s">
-        <v>1568</v>
+        <v>1564</v>
       </c>
       <c r="C118" s="81" t="s">
         <v>920</v>
@@ -58537,13 +58567,13 @@
         <v>1560</v>
       </c>
       <c r="S118" s="43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T118" s="63" t="s">
         <v>1555</v>
       </c>
       <c r="U118" s="43" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="V118" s="61" t="s">
         <v>9</v>
@@ -58567,7 +58597,7 @@
         <v>1561</v>
       </c>
       <c r="AC118" s="64">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AD118" s="63" t="s">
         <v>1562</v>
@@ -58653,7 +58683,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="80" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="C119" s="81" t="s">
         <v>920</v>
@@ -58680,7 +58710,7 @@
         <v>86</v>
       </c>
       <c r="K119" s="64" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="L119" s="61" t="s">
         <v>135</v>
@@ -58698,7 +58728,7 @@
         <v>1558</v>
       </c>
       <c r="Q119" s="64" t="s">
-        <v>1573</v>
+        <v>1567</v>
       </c>
       <c r="R119" s="63" t="s">
         <v>1560</v>
@@ -58710,7 +58740,7 @@
         <v>1555</v>
       </c>
       <c r="U119" s="43" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="V119" s="61" t="s">
         <v>9</v>
@@ -58734,7 +58764,7 @@
         <v>1561</v>
       </c>
       <c r="AC119" s="64">
-        <v>2250</v>
+        <v>900</v>
       </c>
       <c r="AD119" s="63" t="s">
         <v>1562</v>
@@ -58820,7 +58850,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="80" t="s">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="C120" s="81" t="s">
         <v>920</v>
@@ -58871,13 +58901,13 @@
         <v>1560</v>
       </c>
       <c r="S120" s="43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T120" s="63" t="s">
         <v>1555</v>
       </c>
       <c r="U120" s="43" t="s">
-        <v>1575</v>
+        <v>1571</v>
       </c>
       <c r="V120" s="61" t="s">
         <v>9</v>
@@ -58901,7 +58931,7 @@
         <v>1561</v>
       </c>
       <c r="AC120" s="64">
-        <v>2700</v>
+        <v>2250</v>
       </c>
       <c r="AD120" s="63" t="s">
         <v>1562</v>
@@ -58987,7 +59017,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="80" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="C121" s="81" t="s">
         <v>920</v>
@@ -59038,13 +59068,13 @@
         <v>1560</v>
       </c>
       <c r="S121" s="43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T121" s="63" t="s">
         <v>1555</v>
       </c>
       <c r="U121" s="43" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="V121" s="61" t="s">
         <v>9</v>
@@ -59068,7 +59098,7 @@
         <v>1561</v>
       </c>
       <c r="AC121" s="64">
-        <v>3150</v>
+        <v>2700</v>
       </c>
       <c r="AD121" s="63" t="s">
         <v>1562</v>
@@ -59154,7 +59184,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="80" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="C122" s="81" t="s">
         <v>920</v>
@@ -59205,13 +59235,13 @@
         <v>1560</v>
       </c>
       <c r="S122" s="43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T122" s="63" t="s">
         <v>1555</v>
       </c>
       <c r="U122" s="43" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="V122" s="61" t="s">
         <v>9</v>
@@ -59235,7 +59265,7 @@
         <v>1561</v>
       </c>
       <c r="AC122" s="64">
-        <v>3600</v>
+        <v>3150</v>
       </c>
       <c r="AD122" s="63" t="s">
         <v>1562</v>
@@ -59321,7 +59351,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="80" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="C123" s="81" t="s">
         <v>920</v>
@@ -59348,7 +59378,7 @@
         <v>86</v>
       </c>
       <c r="K123" s="64" t="s">
-        <v>1582</v>
+        <v>1572</v>
       </c>
       <c r="L123" s="61" t="s">
         <v>135</v>
@@ -59366,19 +59396,19 @@
         <v>1558</v>
       </c>
       <c r="Q123" s="64" t="s">
-        <v>1583</v>
+        <v>1573</v>
       </c>
       <c r="R123" s="63" t="s">
         <v>1560</v>
       </c>
       <c r="S123" s="43">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T123" s="63" t="s">
         <v>1555</v>
       </c>
       <c r="U123" s="43" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="V123" s="61" t="s">
         <v>9</v>
@@ -59402,7 +59432,7 @@
         <v>1561</v>
       </c>
       <c r="AC123" s="64">
-        <v>5000</v>
+        <v>3600</v>
       </c>
       <c r="AD123" s="63" t="s">
         <v>1562</v>
@@ -59488,7 +59518,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="80" t="s">
-        <v>1584</v>
+        <v>1580</v>
       </c>
       <c r="C124" s="81" t="s">
         <v>920</v>
@@ -59539,13 +59569,13 @@
         <v>1560</v>
       </c>
       <c r="S124" s="43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T124" s="63" t="s">
         <v>1555</v>
       </c>
       <c r="U124" s="43" t="s">
-        <v>1585</v>
+        <v>1581</v>
       </c>
       <c r="V124" s="61" t="s">
         <v>9</v>
@@ -59569,7 +59599,7 @@
         <v>1561</v>
       </c>
       <c r="AC124" s="64">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="AD124" s="63" t="s">
         <v>1562</v>
@@ -59655,7 +59685,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="80" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="C125" s="81" t="s">
         <v>920</v>
@@ -59706,13 +59736,13 @@
         <v>1560</v>
       </c>
       <c r="S125" s="43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T125" s="63" t="s">
         <v>1555</v>
       </c>
       <c r="U125" s="43" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="V125" s="61" t="s">
         <v>9</v>
@@ -59736,7 +59766,7 @@
         <v>1561</v>
       </c>
       <c r="AC125" s="64">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="AD125" s="63" t="s">
         <v>1562</v>
@@ -59822,7 +59852,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="80" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="C126" s="81" t="s">
         <v>920</v>
@@ -59849,7 +59879,7 @@
         <v>86</v>
       </c>
       <c r="K126" s="64" t="s">
-        <v>1590</v>
+        <v>1582</v>
       </c>
       <c r="L126" s="61" t="s">
         <v>135</v>
@@ -59867,7 +59897,7 @@
         <v>1558</v>
       </c>
       <c r="Q126" s="64" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="R126" s="63" t="s">
         <v>1560</v>
@@ -59879,7 +59909,7 @@
         <v>1555</v>
       </c>
       <c r="U126" s="43" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="V126" s="61" t="s">
         <v>9</v>
@@ -59902,14 +59932,14 @@
       <c r="AB126" s="63" t="s">
         <v>1561</v>
       </c>
-      <c r="AC126" s="64" t="s">
-        <v>1592</v>
+      <c r="AC126" s="64">
+        <v>7000</v>
       </c>
       <c r="AD126" s="63" t="s">
         <v>1562</v>
       </c>
       <c r="AE126" s="64">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AF126" s="61" t="s">
         <v>9</v>
@@ -59989,7 +60019,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="80" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="C127" s="81" t="s">
         <v>920</v>
@@ -60016,7 +60046,7 @@
         <v>86</v>
       </c>
       <c r="K127" s="64" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="L127" s="61" t="s">
         <v>135</v>
@@ -60046,7 +60076,7 @@
         <v>1555</v>
       </c>
       <c r="U127" s="43" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="V127" s="61" t="s">
         <v>9</v>
@@ -60076,7 +60106,7 @@
         <v>1562</v>
       </c>
       <c r="AE127" s="64">
-        <v>3700</v>
+        <v>1800</v>
       </c>
       <c r="AF127" s="61" t="s">
         <v>9</v>
@@ -60148,47 +60178,214 @@
         <v>9</v>
       </c>
       <c r="BC127" s="45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:55" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="84">
+        <v>128</v>
+      </c>
+      <c r="B128" s="80" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C128" s="81" t="s">
+        <v>920</v>
+      </c>
+      <c r="D128" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="G128" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H128" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I128" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="J128" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="K128" s="64" t="s">
+        <v>1595</v>
+      </c>
+      <c r="L128" s="61" t="s">
+        <v>135</v>
+      </c>
+      <c r="M128" s="64" t="s">
+        <v>1597</v>
+      </c>
+      <c r="N128" s="61" t="s">
+        <v>136</v>
+      </c>
+      <c r="O128" s="45" t="s">
+        <v>1598</v>
+      </c>
+      <c r="P128" s="63" t="s">
+        <v>1558</v>
+      </c>
+      <c r="Q128" s="64" t="s">
+        <v>1591</v>
+      </c>
+      <c r="R128" s="63" t="s">
+        <v>1560</v>
+      </c>
+      <c r="S128" s="43">
+        <v>8</v>
+      </c>
+      <c r="T128" s="63" t="s">
+        <v>1555</v>
+      </c>
+      <c r="U128" s="43" t="s">
+        <v>1594</v>
+      </c>
+      <c r="V128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="W128" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="X128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y128" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z128" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA128" s="45" t="s">
+        <v>1596</v>
+      </c>
+      <c r="AB128" s="63" t="s">
+        <v>1561</v>
+      </c>
+      <c r="AC128" s="64" t="s">
+        <v>1592</v>
+      </c>
+      <c r="AD128" s="63" t="s">
+        <v>1562</v>
+      </c>
+      <c r="AE128" s="64">
+        <v>3700</v>
+      </c>
+      <c r="AF128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG128" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI128" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK128" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM128" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO128" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP128" s="63" t="s">
+        <v>1563</v>
+      </c>
+      <c r="AQ128" s="64" t="s">
+        <v>1599</v>
+      </c>
+      <c r="AR128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS128" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU128" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW128" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AX128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY128" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA128" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB128" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="BC128" s="45" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B2 B3:B34 A116:B1048576 A3:A115">
-    <cfRule type="cellIs" dxfId="13" priority="30" operator="equal">
+  <conditionalFormatting sqref="A129:B1048576 A1:B2 B3:B35 B117:B128 A3:A128">
+    <cfRule type="cellIs" dxfId="0" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B60">
-    <cfRule type="duplicateValues" dxfId="12" priority="23"/>
-    <cfRule type="cellIs" dxfId="11" priority="24" operator="equal">
+  <conditionalFormatting sqref="B36:B61">
+    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
+    <cfRule type="cellIs" dxfId="12" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B61:B69">
-    <cfRule type="duplicateValues" dxfId="10" priority="22"/>
+  <conditionalFormatting sqref="B62:B70">
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B61:B115">
-    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
+  <conditionalFormatting sqref="B62:B116">
+    <cfRule type="cellIs" dxfId="10" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B70:B77">
-    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
+  <conditionalFormatting sqref="B71:B78">
+    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B78:B89">
-    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
+  <conditionalFormatting sqref="B79:B90">
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B78:B115">
-    <cfRule type="duplicateValues" dxfId="6" priority="18"/>
+  <conditionalFormatting sqref="B79:B116">
+    <cfRule type="duplicateValues" dxfId="7" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B116:B1048576 B1:B34">
-    <cfRule type="duplicateValues" dxfId="5" priority="27"/>
+  <conditionalFormatting sqref="B117:B1048576 B1:B35">
+    <cfRule type="duplicateValues" dxfId="6" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B116:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="25"/>
+  <conditionalFormatting sqref="B117:B1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:XFD1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -60256,15 +60453,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576 C2:G2">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/ARQU/Ontologia_ARQUI.xlsx
+++ b/Versão5/ARQU/Ontologia_ARQUI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783AA85E-99FA-45E7-94C5-972C637FD663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834D79ED-E936-478C-B9C9-A066F2250C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="B18" s="32">
         <f ca="1">NOW()</f>
-        <v>46213.752953240742</v>
+        <v>46214.359736689818</v>
       </c>
       <c r="C18" s="59" t="s">
         <v>1364</v>
@@ -38903,60 +38903,60 @@
   <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.3046875" style="85" customWidth="1"/>
-    <col min="2" max="2" width="9.3828125" style="50" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.69140625" style="50" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" style="50" customWidth="1"/>
-    <col min="9" max="9" width="6.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6" style="50" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="77.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.53515625" style="50" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.61328125" style="50" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.07421875" style="50" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.84375" style="50" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.69140625" style="50" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.4609375" style="50" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.15234375" style="50" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.07421875" style="50" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="57.4609375" style="50" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.765625" style="50" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" style="50" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.15234375" style="50" customWidth="1"/>
-    <col min="16" max="16" width="12.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.921875" style="50" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.15234375" style="50" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.07421875" style="50" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.84375" style="49" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.69140625" style="50" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.84375" style="49" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7" style="50" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.84375" style="49" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.61328125" style="50" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.84375" style="49" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.4609375" style="50" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.15234375" style="49" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.921875" style="50" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.84375" style="49" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.61328125" style="50" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.84375" style="50" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="6.15234375" style="50" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.69140625" style="50" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.53515625" style="50" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.69140625" style="50" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12" style="50" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="2.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.4609375" style="50" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="3.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12" style="50" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.4609375" style="50" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="3.84375" style="50" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="11" style="50" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="3.84375" style="50" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="11.3046875" style="50" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="3.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.3046875" style="50" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="7.921875" style="50" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="3.84375" style="50" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="4.3046875" style="50" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="3.84375" style="50" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="4.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="3.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="3.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="4.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="3.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="4.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="3.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="4.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="3.84375" style="50" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.3046875" style="50" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="3.84375" style="50" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.921875" style="50" customWidth="1"/>
+    <col min="44" max="44" width="2.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="2.23046875" style="50" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="2.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="2.23046875" style="50" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="2.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="2.23046875" style="50" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="2.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="2.23046875" style="50" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="2.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="2.23046875" style="50" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="2.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="2.23046875" style="50" bestFit="1" customWidth="1"/>
     <col min="56" max="16384" width="9.3046875" style="50"/>
   </cols>
   <sheetData>
